--- a/uploads/excel_format/bank_statement_format.xlsx
+++ b/uploads/excel_format/bank_statement_format.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
@@ -57,7 +57,7 @@
     <definedName name="VirudhunagarList">Sheet2!$AJ$2:$AJ$11</definedName>
     <definedName name="YanamList">Sheet2!$AN$2:$AN$5</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="343">
   <si>
     <t>State</t>
   </si>
@@ -1083,12 +1083,6 @@
     <t>YanamList</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Transaction ID</t>
-  </si>
-  <si>
     <t>Credit</t>
   </si>
   <si>
@@ -1099,13 +1093,16 @@
   </si>
   <si>
     <t>Narration</t>
+  </si>
+  <si>
+    <t>Datetime</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,38 +1414,32 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1" t="s">
         <v>338</v>
       </c>
-      <c r="B1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>339</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>340</v>
-      </c>
-      <c r="E1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F1" t="s">
-        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -1457,15 +1448,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AO33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +1575,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1703,7 +1694,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1822,7 +1813,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1938,7 +1929,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41">
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -2054,7 +2045,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -2149,7 +2140,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41">
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -2238,7 +2229,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41">
       <c r="B8" t="s">
         <v>10</v>
       </c>
@@ -2315,7 +2306,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41">
       <c r="B9" t="s">
         <v>11</v>
       </c>
@@ -2389,7 +2380,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -2448,7 +2439,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41">
       <c r="B11" t="s">
         <v>13</v>
       </c>
@@ -2489,7 +2480,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41">
       <c r="B12" t="s">
         <v>14</v>
       </c>
@@ -2509,7 +2500,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41">
       <c r="B13" t="s">
         <v>15</v>
       </c>
@@ -2526,7 +2517,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -2537,7 +2528,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41">
       <c r="B15" t="s">
         <v>17</v>
       </c>
@@ -2545,7 +2536,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -2553,87 +2544,87 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2">
       <c r="B17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2">
       <c r="B21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2">
       <c r="B23" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2">
       <c r="B24" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2">
       <c r="B25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2">
       <c r="B26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2">
       <c r="B27" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2">
       <c r="B28" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2">
       <c r="B29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2">
       <c r="B30" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2">
       <c r="B31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2">
       <c r="B32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2">
       <c r="B33" t="s">
         <v>35</v>
       </c>

--- a/uploads/excel_format/bank_statement_format.xlsx
+++ b/uploads/excel_format/bank_statement_format.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Bank Statement" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bank Statement'!$B$1:$E$1</definedName>
     <definedName name="AriyalurList">Sheet2!$E$2:$E$5</definedName>
     <definedName name="Bhuvanagiri">Sheet2!$H$2:$H$11</definedName>
-    <definedName name="BryanList">#REF!</definedName>
+    <definedName name="BryanList">'Bank Statement'!#REF!</definedName>
     <definedName name="ChennaiList">Sheet2!$F$2:$F$16</definedName>
     <definedName name="CoimbatoreList">Sheet2!$G$2:$G$12</definedName>
     <definedName name="CuddaloreList">Sheet2!$H$2:$H$11</definedName>
@@ -29,12 +30,12 @@
     <definedName name="MaheList">Sheet2!$AL$2:$AL$5</definedName>
     <definedName name="NagapattinamList">Sheet2!$Q$2:$Q$9</definedName>
     <definedName name="NamakkalList">Sheet2!$R$2:$R$9</definedName>
-    <definedName name="NameList">#REF!</definedName>
+    <definedName name="NameList">'Bank Statement'!#REF!</definedName>
     <definedName name="NilgirisList">Sheet2!$S$2:$S$7</definedName>
     <definedName name="PerambalurList">Sheet2!$T$2:$T$5</definedName>
     <definedName name="PondicherryList">Sheet2!$C$2:$C$5</definedName>
     <definedName name="PondicherryTalukList">Sheet2!#REF!</definedName>
-    <definedName name="ProductList">#REF!</definedName>
+    <definedName name="ProductList">'Bank Statement'!#REF!</definedName>
     <definedName name="PuducherryList">Sheet2!$AM$2:$AM$5</definedName>
     <definedName name="PudukkottaiList">Sheet2!$U$2:$U$13</definedName>
     <definedName name="RamanathapuramList">Sheet2!$V$2:$V$10</definedName>
@@ -58,16 +59,11 @@
     <definedName name="YanamList">Sheet2!$AN$2:$AN$5</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="346">
   <si>
     <t>State</t>
   </si>
@@ -1095,14 +1091,23 @@
     <t>Narration</t>
   </si>
   <si>
-    <t>Datetime</t>
+    <t>Copied Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Date Format</t>
+  </si>
+  <si>
+    <t>=TEXT(G2,"yyyy-mm-dd hh:mm:ss")'</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1118,13 +1123,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1136,24 +1157,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1414,7 +1447,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1422,28 +1455,4447 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:XFC880"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="97.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26" style="6" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="9" width="33.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9 16383:16383" s="2" customFormat="1">
+      <c r="A1" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="B1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E1" t="s">
-        <v>340</v>
-      </c>
+      <c r="H1" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="XFC1" s="3"/>
+    </row>
+    <row r="2" spans="1:9 16383:16383">
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3" spans="1:9 16383:16383">
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:9 16383:16383">
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:9 16383:16383">
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+    </row>
+    <row r="6" spans="1:9 16383:16383">
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:9 16383:16383">
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+    </row>
+    <row r="8" spans="1:9 16383:16383">
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+    </row>
+    <row r="9" spans="1:9 16383:16383">
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+    </row>
+    <row r="10" spans="1:9 16383:16383">
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+    </row>
+    <row r="11" spans="1:9 16383:16383">
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+    </row>
+    <row r="12" spans="1:9 16383:16383">
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+    </row>
+    <row r="13" spans="1:9 16383:16383">
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+    </row>
+    <row r="14" spans="1:9 16383:16383">
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+    </row>
+    <row r="15" spans="1:9 16383:16383">
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+    </row>
+    <row r="16" spans="1:9 16383:16383">
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+    </row>
+    <row r="18" spans="3:5">
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+    </row>
+    <row r="19" spans="3:5">
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+    </row>
+    <row r="20" spans="3:5">
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+    </row>
+    <row r="21" spans="3:5">
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+    </row>
+    <row r="22" spans="3:5">
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+    </row>
+    <row r="23" spans="3:5">
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="3:5">
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+    </row>
+    <row r="25" spans="3:5">
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+    </row>
+    <row r="26" spans="3:5">
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+    </row>
+    <row r="27" spans="3:5">
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+    </row>
+    <row r="28" spans="3:5">
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+    </row>
+    <row r="29" spans="3:5">
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+    </row>
+    <row r="30" spans="3:5">
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+    </row>
+    <row r="31" spans="3:5">
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+    </row>
+    <row r="32" spans="3:5">
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+    </row>
+    <row r="33" spans="3:5">
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+    </row>
+    <row r="34" spans="3:5">
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+    </row>
+    <row r="35" spans="3:5">
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+    </row>
+    <row r="36" spans="3:5">
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+    </row>
+    <row r="37" spans="3:5">
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="3:5">
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+    </row>
+    <row r="39" spans="3:5">
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+    </row>
+    <row r="40" spans="3:5">
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+    </row>
+    <row r="41" spans="3:5">
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="3:5">
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+    </row>
+    <row r="43" spans="3:5">
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="3:5">
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+    </row>
+    <row r="45" spans="3:5">
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+    </row>
+    <row r="46" spans="3:5">
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+    </row>
+    <row r="47" spans="3:5">
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+    </row>
+    <row r="48" spans="3:5">
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+    </row>
+    <row r="49" spans="3:5">
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+    </row>
+    <row r="50" spans="3:5">
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+    </row>
+    <row r="51" spans="3:5">
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+    </row>
+    <row r="52" spans="3:5">
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+    </row>
+    <row r="53" spans="3:5">
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="3:5">
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="3:5">
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="3:5">
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="3:5">
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+    </row>
+    <row r="58" spans="3:5">
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+    </row>
+    <row r="59" spans="3:5">
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="3:5">
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+    </row>
+    <row r="61" spans="3:5">
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+    </row>
+    <row r="62" spans="3:5">
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+    </row>
+    <row r="63" spans="3:5">
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+    </row>
+    <row r="64" spans="3:5">
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+    </row>
+    <row r="65" spans="3:5">
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+    </row>
+    <row r="66" spans="3:5">
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+    </row>
+    <row r="67" spans="3:5">
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
+    </row>
+    <row r="68" spans="3:5">
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+    </row>
+    <row r="69" spans="3:5">
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+    </row>
+    <row r="70" spans="3:5">
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70"/>
+    </row>
+    <row r="71" spans="3:5">
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+    </row>
+    <row r="72" spans="3:5">
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+    </row>
+    <row r="73" spans="3:5">
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73"/>
+    </row>
+    <row r="74" spans="3:5">
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
+    </row>
+    <row r="75" spans="3:5">
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
+    </row>
+    <row r="76" spans="3:5">
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
+    </row>
+    <row r="77" spans="3:5">
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+    </row>
+    <row r="78" spans="3:5">
+      <c r="C78"/>
+      <c r="D78"/>
+      <c r="E78"/>
+    </row>
+    <row r="79" spans="3:5">
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+    </row>
+    <row r="80" spans="3:5">
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+    </row>
+    <row r="81" spans="3:5">
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+    </row>
+    <row r="82" spans="3:5">
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+    </row>
+    <row r="83" spans="3:5">
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+    </row>
+    <row r="84" spans="3:5">
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+    </row>
+    <row r="85" spans="3:5">
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+    </row>
+    <row r="86" spans="3:5">
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+    </row>
+    <row r="87" spans="3:5">
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+    </row>
+    <row r="88" spans="3:5">
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
+    </row>
+    <row r="89" spans="3:5">
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+    </row>
+    <row r="90" spans="3:5">
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+    </row>
+    <row r="91" spans="3:5">
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+    </row>
+    <row r="92" spans="3:5">
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+    </row>
+    <row r="93" spans="3:5">
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
+    </row>
+    <row r="94" spans="3:5">
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+    </row>
+    <row r="95" spans="3:5">
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
+    </row>
+    <row r="96" spans="3:5">
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+    </row>
+    <row r="97" spans="3:5">
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+    </row>
+    <row r="98" spans="3:5">
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
+    </row>
+    <row r="99" spans="3:5">
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+    </row>
+    <row r="100" spans="3:5">
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+    </row>
+    <row r="101" spans="3:5">
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+    </row>
+    <row r="102" spans="3:5">
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+    </row>
+    <row r="103" spans="3:5">
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+    </row>
+    <row r="104" spans="3:5">
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+    </row>
+    <row r="105" spans="3:5">
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+    </row>
+    <row r="106" spans="3:5">
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+    </row>
+    <row r="107" spans="3:5">
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+    </row>
+    <row r="108" spans="3:5">
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+    </row>
+    <row r="109" spans="3:5">
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+    </row>
+    <row r="110" spans="3:5">
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+    </row>
+    <row r="111" spans="3:5">
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+    </row>
+    <row r="112" spans="3:5">
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+    </row>
+    <row r="113" spans="3:5">
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+    </row>
+    <row r="114" spans="3:5">
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+    </row>
+    <row r="115" spans="3:5">
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+    </row>
+    <row r="116" spans="3:5">
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+    </row>
+    <row r="117" spans="3:5">
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+    </row>
+    <row r="118" spans="3:5">
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+    </row>
+    <row r="119" spans="3:5">
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+    </row>
+    <row r="120" spans="3:5">
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+    </row>
+    <row r="121" spans="3:5">
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+    </row>
+    <row r="122" spans="3:5">
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+    </row>
+    <row r="123" spans="3:5">
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+    </row>
+    <row r="124" spans="3:5">
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+    </row>
+    <row r="125" spans="3:5">
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
+    </row>
+    <row r="126" spans="3:5">
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
+    </row>
+    <row r="127" spans="3:5">
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+    </row>
+    <row r="128" spans="3:5">
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128"/>
+    </row>
+    <row r="129" spans="3:5">
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+    </row>
+    <row r="130" spans="3:5">
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+    </row>
+    <row r="131" spans="3:5">
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+    </row>
+    <row r="132" spans="3:5">
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="E132"/>
+    </row>
+    <row r="133" spans="3:5">
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="E133"/>
+    </row>
+    <row r="134" spans="3:5">
+      <c r="C134"/>
+      <c r="D134"/>
+      <c r="E134"/>
+    </row>
+    <row r="135" spans="3:5">
+      <c r="C135"/>
+      <c r="D135"/>
+      <c r="E135"/>
+    </row>
+    <row r="136" spans="3:5">
+      <c r="C136"/>
+      <c r="D136"/>
+      <c r="E136"/>
+    </row>
+    <row r="137" spans="3:5">
+      <c r="C137"/>
+      <c r="D137"/>
+      <c r="E137"/>
+    </row>
+    <row r="138" spans="3:5">
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="E138"/>
+    </row>
+    <row r="139" spans="3:5">
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139"/>
+    </row>
+    <row r="140" spans="3:5">
+      <c r="C140"/>
+      <c r="D140"/>
+      <c r="E140"/>
+    </row>
+    <row r="141" spans="3:5">
+      <c r="C141"/>
+      <c r="D141"/>
+      <c r="E141"/>
+    </row>
+    <row r="142" spans="3:5">
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="E142"/>
+    </row>
+    <row r="143" spans="3:5">
+      <c r="C143"/>
+      <c r="D143"/>
+      <c r="E143"/>
+    </row>
+    <row r="144" spans="3:5">
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="E144"/>
+    </row>
+    <row r="145" spans="3:5">
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="E145"/>
+    </row>
+    <row r="146" spans="3:5">
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="E146"/>
+    </row>
+    <row r="147" spans="3:5">
+      <c r="C147"/>
+      <c r="D147"/>
+      <c r="E147"/>
+    </row>
+    <row r="148" spans="3:5">
+      <c r="C148"/>
+      <c r="D148"/>
+      <c r="E148"/>
+    </row>
+    <row r="149" spans="3:5">
+      <c r="C149"/>
+      <c r="D149"/>
+      <c r="E149"/>
+    </row>
+    <row r="150" spans="3:5">
+      <c r="C150"/>
+      <c r="D150"/>
+      <c r="E150"/>
+    </row>
+    <row r="151" spans="3:5">
+      <c r="C151"/>
+      <c r="D151"/>
+      <c r="E151"/>
+    </row>
+    <row r="152" spans="3:5">
+      <c r="C152"/>
+      <c r="D152"/>
+      <c r="E152"/>
+    </row>
+    <row r="153" spans="3:5">
+      <c r="C153"/>
+      <c r="D153"/>
+      <c r="E153"/>
+    </row>
+    <row r="154" spans="3:5">
+      <c r="C154"/>
+      <c r="D154"/>
+      <c r="E154"/>
+    </row>
+    <row r="155" spans="3:5">
+      <c r="C155"/>
+      <c r="D155"/>
+      <c r="E155"/>
+    </row>
+    <row r="156" spans="3:5">
+      <c r="C156"/>
+      <c r="D156"/>
+      <c r="E156"/>
+    </row>
+    <row r="157" spans="3:5">
+      <c r="C157"/>
+      <c r="D157"/>
+      <c r="E157"/>
+    </row>
+    <row r="158" spans="3:5">
+      <c r="C158"/>
+      <c r="D158"/>
+      <c r="E158"/>
+    </row>
+    <row r="159" spans="3:5">
+      <c r="C159"/>
+      <c r="D159"/>
+      <c r="E159"/>
+    </row>
+    <row r="160" spans="3:5">
+      <c r="C160"/>
+      <c r="D160"/>
+      <c r="E160"/>
+    </row>
+    <row r="161" spans="3:5">
+      <c r="C161"/>
+      <c r="D161"/>
+      <c r="E161"/>
+    </row>
+    <row r="162" spans="3:5">
+      <c r="C162"/>
+      <c r="D162"/>
+      <c r="E162"/>
+    </row>
+    <row r="163" spans="3:5">
+      <c r="C163"/>
+      <c r="D163"/>
+      <c r="E163"/>
+    </row>
+    <row r="164" spans="3:5">
+      <c r="C164"/>
+      <c r="D164"/>
+      <c r="E164"/>
+    </row>
+    <row r="165" spans="3:5">
+      <c r="C165"/>
+      <c r="D165"/>
+      <c r="E165"/>
+    </row>
+    <row r="166" spans="3:5">
+      <c r="C166"/>
+      <c r="D166"/>
+      <c r="E166"/>
+    </row>
+    <row r="167" spans="3:5">
+      <c r="C167"/>
+      <c r="D167"/>
+      <c r="E167"/>
+    </row>
+    <row r="168" spans="3:5">
+      <c r="C168"/>
+      <c r="D168"/>
+      <c r="E168"/>
+    </row>
+    <row r="169" spans="3:5">
+      <c r="C169"/>
+      <c r="D169"/>
+      <c r="E169"/>
+    </row>
+    <row r="170" spans="3:5">
+      <c r="C170"/>
+      <c r="D170"/>
+      <c r="E170"/>
+    </row>
+    <row r="171" spans="3:5">
+      <c r="C171"/>
+      <c r="D171"/>
+      <c r="E171"/>
+    </row>
+    <row r="172" spans="3:5">
+      <c r="C172"/>
+      <c r="D172"/>
+      <c r="E172"/>
+    </row>
+    <row r="173" spans="3:5">
+      <c r="C173"/>
+      <c r="D173"/>
+      <c r="E173"/>
+    </row>
+    <row r="174" spans="3:5">
+      <c r="C174"/>
+      <c r="D174"/>
+      <c r="E174"/>
+    </row>
+    <row r="175" spans="3:5">
+      <c r="C175"/>
+      <c r="D175"/>
+      <c r="E175"/>
+    </row>
+    <row r="176" spans="3:5">
+      <c r="C176"/>
+      <c r="D176"/>
+      <c r="E176"/>
+    </row>
+    <row r="177" spans="3:5">
+      <c r="C177"/>
+      <c r="D177"/>
+      <c r="E177"/>
+    </row>
+    <row r="178" spans="3:5">
+      <c r="C178"/>
+      <c r="D178"/>
+      <c r="E178"/>
+    </row>
+    <row r="179" spans="3:5">
+      <c r="C179"/>
+      <c r="D179"/>
+      <c r="E179"/>
+    </row>
+    <row r="180" spans="3:5">
+      <c r="C180"/>
+      <c r="D180"/>
+      <c r="E180"/>
+    </row>
+    <row r="181" spans="3:5">
+      <c r="C181"/>
+      <c r="D181"/>
+      <c r="E181"/>
+    </row>
+    <row r="182" spans="3:5">
+      <c r="C182"/>
+      <c r="D182"/>
+      <c r="E182"/>
+    </row>
+    <row r="183" spans="3:5">
+      <c r="C183"/>
+      <c r="D183"/>
+      <c r="E183"/>
+    </row>
+    <row r="184" spans="3:5">
+      <c r="C184"/>
+      <c r="D184"/>
+      <c r="E184"/>
+    </row>
+    <row r="185" spans="3:5">
+      <c r="C185"/>
+      <c r="D185"/>
+      <c r="E185"/>
+    </row>
+    <row r="186" spans="3:5">
+      <c r="C186"/>
+      <c r="D186"/>
+      <c r="E186"/>
+    </row>
+    <row r="187" spans="3:5">
+      <c r="C187"/>
+      <c r="D187"/>
+      <c r="E187"/>
+    </row>
+    <row r="188" spans="3:5">
+      <c r="C188"/>
+      <c r="D188"/>
+      <c r="E188"/>
+    </row>
+    <row r="189" spans="3:5">
+      <c r="C189"/>
+      <c r="D189"/>
+      <c r="E189"/>
+    </row>
+    <row r="190" spans="3:5">
+      <c r="C190"/>
+      <c r="D190"/>
+      <c r="E190"/>
+    </row>
+    <row r="191" spans="3:5">
+      <c r="C191"/>
+      <c r="D191"/>
+      <c r="E191"/>
+    </row>
+    <row r="192" spans="3:5">
+      <c r="C192"/>
+      <c r="D192"/>
+      <c r="E192"/>
+    </row>
+    <row r="193" spans="3:5">
+      <c r="C193"/>
+      <c r="D193"/>
+      <c r="E193"/>
+    </row>
+    <row r="194" spans="3:5">
+      <c r="C194"/>
+      <c r="D194"/>
+      <c r="E194"/>
+    </row>
+    <row r="195" spans="3:5">
+      <c r="C195"/>
+      <c r="D195"/>
+      <c r="E195"/>
+    </row>
+    <row r="196" spans="3:5">
+      <c r="C196"/>
+      <c r="D196"/>
+      <c r="E196"/>
+    </row>
+    <row r="197" spans="3:5">
+      <c r="C197"/>
+      <c r="D197"/>
+      <c r="E197"/>
+    </row>
+    <row r="198" spans="3:5">
+      <c r="C198"/>
+      <c r="D198"/>
+      <c r="E198"/>
+    </row>
+    <row r="199" spans="3:5">
+      <c r="C199"/>
+      <c r="D199"/>
+      <c r="E199"/>
+    </row>
+    <row r="200" spans="3:5">
+      <c r="C200"/>
+      <c r="D200"/>
+      <c r="E200"/>
+    </row>
+    <row r="201" spans="3:5">
+      <c r="C201"/>
+      <c r="D201"/>
+      <c r="E201"/>
+    </row>
+    <row r="202" spans="3:5">
+      <c r="C202"/>
+      <c r="D202"/>
+      <c r="E202"/>
+    </row>
+    <row r="203" spans="3:5">
+      <c r="C203"/>
+      <c r="D203"/>
+      <c r="E203"/>
+    </row>
+    <row r="204" spans="3:5">
+      <c r="C204"/>
+      <c r="D204"/>
+      <c r="E204"/>
+    </row>
+    <row r="205" spans="3:5">
+      <c r="C205"/>
+      <c r="D205"/>
+      <c r="E205"/>
+    </row>
+    <row r="206" spans="3:5">
+      <c r="C206"/>
+      <c r="D206"/>
+      <c r="E206"/>
+    </row>
+    <row r="207" spans="3:5">
+      <c r="C207"/>
+      <c r="D207"/>
+      <c r="E207"/>
+    </row>
+    <row r="208" spans="3:5">
+      <c r="C208"/>
+      <c r="D208"/>
+      <c r="E208"/>
+    </row>
+    <row r="209" spans="3:5">
+      <c r="C209"/>
+      <c r="D209"/>
+      <c r="E209"/>
+    </row>
+    <row r="210" spans="3:5">
+      <c r="C210"/>
+      <c r="D210"/>
+      <c r="E210"/>
+    </row>
+    <row r="211" spans="3:5">
+      <c r="C211"/>
+      <c r="D211"/>
+      <c r="E211"/>
+    </row>
+    <row r="212" spans="3:5">
+      <c r="C212"/>
+      <c r="D212"/>
+      <c r="E212"/>
+    </row>
+    <row r="213" spans="3:5">
+      <c r="C213"/>
+      <c r="D213"/>
+      <c r="E213"/>
+    </row>
+    <row r="214" spans="3:5">
+      <c r="C214"/>
+      <c r="D214"/>
+      <c r="E214"/>
+    </row>
+    <row r="215" spans="3:5">
+      <c r="C215"/>
+      <c r="D215"/>
+      <c r="E215"/>
+    </row>
+    <row r="216" spans="3:5">
+      <c r="C216"/>
+      <c r="D216"/>
+      <c r="E216"/>
+    </row>
+    <row r="217" spans="3:5">
+      <c r="C217"/>
+      <c r="D217"/>
+      <c r="E217"/>
+    </row>
+    <row r="218" spans="3:5">
+      <c r="C218"/>
+      <c r="D218"/>
+      <c r="E218"/>
+    </row>
+    <row r="219" spans="3:5">
+      <c r="C219"/>
+      <c r="D219"/>
+      <c r="E219"/>
+    </row>
+    <row r="220" spans="3:5">
+      <c r="C220"/>
+      <c r="D220"/>
+      <c r="E220"/>
+    </row>
+    <row r="221" spans="3:5">
+      <c r="C221"/>
+      <c r="D221"/>
+      <c r="E221"/>
+    </row>
+    <row r="222" spans="3:5">
+      <c r="C222"/>
+      <c r="D222"/>
+      <c r="E222"/>
+    </row>
+    <row r="223" spans="3:5">
+      <c r="C223"/>
+      <c r="D223"/>
+      <c r="E223"/>
+    </row>
+    <row r="224" spans="3:5">
+      <c r="C224"/>
+      <c r="D224"/>
+      <c r="E224"/>
+    </row>
+    <row r="225" spans="3:5">
+      <c r="C225"/>
+      <c r="D225"/>
+      <c r="E225"/>
+    </row>
+    <row r="226" spans="3:5">
+      <c r="C226"/>
+      <c r="D226"/>
+      <c r="E226"/>
+    </row>
+    <row r="227" spans="3:5">
+      <c r="C227"/>
+      <c r="D227"/>
+      <c r="E227"/>
+    </row>
+    <row r="228" spans="3:5">
+      <c r="C228"/>
+      <c r="D228"/>
+      <c r="E228"/>
+    </row>
+    <row r="229" spans="3:5">
+      <c r="C229"/>
+      <c r="D229"/>
+      <c r="E229"/>
+    </row>
+    <row r="230" spans="3:5">
+      <c r="C230"/>
+      <c r="D230"/>
+      <c r="E230"/>
+    </row>
+    <row r="231" spans="3:5">
+      <c r="C231"/>
+      <c r="D231"/>
+      <c r="E231"/>
+    </row>
+    <row r="232" spans="3:5">
+      <c r="C232"/>
+      <c r="D232"/>
+      <c r="E232"/>
+    </row>
+    <row r="233" spans="3:5">
+      <c r="C233"/>
+      <c r="D233"/>
+      <c r="E233"/>
+    </row>
+    <row r="234" spans="3:5">
+      <c r="C234"/>
+      <c r="D234"/>
+      <c r="E234"/>
+    </row>
+    <row r="235" spans="3:5">
+      <c r="C235"/>
+      <c r="D235"/>
+      <c r="E235"/>
+    </row>
+    <row r="236" spans="3:5">
+      <c r="C236"/>
+      <c r="D236"/>
+      <c r="E236"/>
+    </row>
+    <row r="237" spans="3:5">
+      <c r="C237"/>
+      <c r="D237"/>
+      <c r="E237"/>
+    </row>
+    <row r="238" spans="3:5">
+      <c r="C238"/>
+      <c r="D238"/>
+      <c r="E238"/>
+    </row>
+    <row r="239" spans="3:5">
+      <c r="C239"/>
+      <c r="D239"/>
+      <c r="E239"/>
+    </row>
+    <row r="240" spans="3:5">
+      <c r="C240"/>
+      <c r="D240"/>
+      <c r="E240"/>
+    </row>
+    <row r="241" spans="3:5">
+      <c r="C241"/>
+      <c r="D241"/>
+      <c r="E241"/>
+    </row>
+    <row r="242" spans="3:5">
+      <c r="C242"/>
+      <c r="D242"/>
+      <c r="E242"/>
+    </row>
+    <row r="243" spans="3:5">
+      <c r="C243"/>
+      <c r="D243"/>
+      <c r="E243"/>
+    </row>
+    <row r="244" spans="3:5">
+      <c r="C244"/>
+      <c r="D244"/>
+      <c r="E244"/>
+    </row>
+    <row r="245" spans="3:5">
+      <c r="C245"/>
+      <c r="D245"/>
+      <c r="E245"/>
+    </row>
+    <row r="246" spans="3:5">
+      <c r="C246"/>
+      <c r="D246"/>
+      <c r="E246"/>
+    </row>
+    <row r="247" spans="3:5">
+      <c r="C247"/>
+      <c r="D247"/>
+      <c r="E247"/>
+    </row>
+    <row r="248" spans="3:5">
+      <c r="C248"/>
+      <c r="D248"/>
+      <c r="E248"/>
+    </row>
+    <row r="249" spans="3:5">
+      <c r="C249"/>
+      <c r="D249"/>
+      <c r="E249"/>
+    </row>
+    <row r="250" spans="3:5">
+      <c r="C250"/>
+      <c r="D250"/>
+      <c r="E250"/>
+    </row>
+    <row r="251" spans="3:5">
+      <c r="C251"/>
+      <c r="D251"/>
+      <c r="E251"/>
+    </row>
+    <row r="252" spans="3:5">
+      <c r="C252"/>
+      <c r="D252"/>
+      <c r="E252"/>
+    </row>
+    <row r="253" spans="3:5">
+      <c r="C253"/>
+      <c r="D253"/>
+      <c r="E253"/>
+    </row>
+    <row r="254" spans="3:5">
+      <c r="C254"/>
+      <c r="D254"/>
+      <c r="E254"/>
+    </row>
+    <row r="255" spans="3:5">
+      <c r="C255"/>
+      <c r="D255"/>
+      <c r="E255"/>
+    </row>
+    <row r="256" spans="3:5">
+      <c r="C256"/>
+      <c r="D256"/>
+      <c r="E256"/>
+    </row>
+    <row r="257" spans="3:5">
+      <c r="C257"/>
+      <c r="D257"/>
+      <c r="E257"/>
+    </row>
+    <row r="258" spans="3:5">
+      <c r="C258"/>
+      <c r="D258"/>
+      <c r="E258"/>
+    </row>
+    <row r="259" spans="3:5">
+      <c r="C259"/>
+      <c r="D259"/>
+      <c r="E259"/>
+    </row>
+    <row r="260" spans="3:5">
+      <c r="C260"/>
+      <c r="D260"/>
+      <c r="E260"/>
+    </row>
+    <row r="261" spans="3:5">
+      <c r="C261"/>
+      <c r="D261"/>
+      <c r="E261"/>
+    </row>
+    <row r="262" spans="3:5">
+      <c r="C262"/>
+      <c r="D262"/>
+      <c r="E262"/>
+    </row>
+    <row r="263" spans="3:5">
+      <c r="C263"/>
+      <c r="D263"/>
+      <c r="E263"/>
+    </row>
+    <row r="264" spans="3:5">
+      <c r="C264"/>
+      <c r="D264"/>
+      <c r="E264"/>
+    </row>
+    <row r="265" spans="3:5">
+      <c r="C265"/>
+      <c r="D265"/>
+      <c r="E265"/>
+    </row>
+    <row r="266" spans="3:5">
+      <c r="C266"/>
+      <c r="D266"/>
+      <c r="E266"/>
+    </row>
+    <row r="267" spans="3:5">
+      <c r="C267"/>
+      <c r="D267"/>
+      <c r="E267"/>
+    </row>
+    <row r="268" spans="3:5">
+      <c r="C268"/>
+      <c r="D268"/>
+      <c r="E268"/>
+    </row>
+    <row r="269" spans="3:5">
+      <c r="C269"/>
+      <c r="D269"/>
+      <c r="E269"/>
+    </row>
+    <row r="270" spans="3:5">
+      <c r="C270"/>
+      <c r="D270"/>
+      <c r="E270"/>
+    </row>
+    <row r="271" spans="3:5">
+      <c r="C271"/>
+      <c r="D271"/>
+      <c r="E271"/>
+    </row>
+    <row r="272" spans="3:5">
+      <c r="C272"/>
+      <c r="D272"/>
+      <c r="E272"/>
+    </row>
+    <row r="273" spans="3:5">
+      <c r="C273"/>
+      <c r="D273"/>
+      <c r="E273"/>
+    </row>
+    <row r="274" spans="3:5">
+      <c r="C274"/>
+      <c r="D274"/>
+      <c r="E274"/>
+    </row>
+    <row r="275" spans="3:5">
+      <c r="C275"/>
+      <c r="D275"/>
+      <c r="E275"/>
+    </row>
+    <row r="276" spans="3:5">
+      <c r="C276"/>
+      <c r="D276"/>
+      <c r="E276"/>
+    </row>
+    <row r="277" spans="3:5">
+      <c r="C277"/>
+      <c r="D277"/>
+      <c r="E277"/>
+    </row>
+    <row r="278" spans="3:5">
+      <c r="C278"/>
+      <c r="D278"/>
+      <c r="E278"/>
+    </row>
+    <row r="279" spans="3:5">
+      <c r="C279"/>
+      <c r="D279"/>
+      <c r="E279"/>
+    </row>
+    <row r="280" spans="3:5">
+      <c r="C280"/>
+      <c r="D280"/>
+      <c r="E280"/>
+    </row>
+    <row r="281" spans="3:5">
+      <c r="C281"/>
+      <c r="D281"/>
+      <c r="E281"/>
+    </row>
+    <row r="282" spans="3:5">
+      <c r="C282"/>
+      <c r="D282"/>
+      <c r="E282"/>
+    </row>
+    <row r="283" spans="3:5">
+      <c r="C283"/>
+      <c r="D283"/>
+      <c r="E283"/>
+    </row>
+    <row r="284" spans="3:5">
+      <c r="C284"/>
+      <c r="D284"/>
+      <c r="E284"/>
+    </row>
+    <row r="285" spans="3:5">
+      <c r="C285"/>
+      <c r="D285"/>
+      <c r="E285"/>
+    </row>
+    <row r="286" spans="3:5">
+      <c r="C286"/>
+      <c r="D286"/>
+      <c r="E286"/>
+    </row>
+    <row r="287" spans="3:5">
+      <c r="C287"/>
+      <c r="D287"/>
+      <c r="E287"/>
+    </row>
+    <row r="288" spans="3:5">
+      <c r="C288"/>
+      <c r="D288"/>
+      <c r="E288"/>
+    </row>
+    <row r="289" spans="3:5">
+      <c r="C289"/>
+      <c r="D289"/>
+      <c r="E289"/>
+    </row>
+    <row r="290" spans="3:5">
+      <c r="C290"/>
+      <c r="D290"/>
+      <c r="E290"/>
+    </row>
+    <row r="291" spans="3:5">
+      <c r="C291"/>
+      <c r="D291"/>
+      <c r="E291"/>
+    </row>
+    <row r="292" spans="3:5">
+      <c r="C292"/>
+      <c r="D292"/>
+      <c r="E292"/>
+    </row>
+    <row r="293" spans="3:5">
+      <c r="C293"/>
+      <c r="D293"/>
+      <c r="E293"/>
+    </row>
+    <row r="294" spans="3:5">
+      <c r="C294"/>
+      <c r="D294"/>
+      <c r="E294"/>
+    </row>
+    <row r="295" spans="3:5">
+      <c r="C295"/>
+      <c r="D295"/>
+      <c r="E295"/>
+    </row>
+    <row r="296" spans="3:5">
+      <c r="C296"/>
+      <c r="D296"/>
+      <c r="E296"/>
+    </row>
+    <row r="297" spans="3:5">
+      <c r="C297"/>
+      <c r="D297"/>
+      <c r="E297"/>
+    </row>
+    <row r="298" spans="3:5">
+      <c r="C298"/>
+      <c r="D298"/>
+      <c r="E298"/>
+    </row>
+    <row r="299" spans="3:5">
+      <c r="C299"/>
+      <c r="D299"/>
+      <c r="E299"/>
+    </row>
+    <row r="300" spans="3:5">
+      <c r="C300"/>
+      <c r="D300"/>
+      <c r="E300"/>
+    </row>
+    <row r="301" spans="3:5">
+      <c r="C301"/>
+      <c r="D301"/>
+      <c r="E301"/>
+    </row>
+    <row r="302" spans="3:5">
+      <c r="C302"/>
+      <c r="D302"/>
+      <c r="E302"/>
+    </row>
+    <row r="303" spans="3:5">
+      <c r="C303"/>
+      <c r="D303"/>
+      <c r="E303"/>
+    </row>
+    <row r="304" spans="3:5">
+      <c r="C304"/>
+      <c r="D304"/>
+      <c r="E304"/>
+    </row>
+    <row r="305" spans="3:5">
+      <c r="C305"/>
+      <c r="D305"/>
+      <c r="E305"/>
+    </row>
+    <row r="306" spans="3:5">
+      <c r="C306"/>
+      <c r="D306"/>
+      <c r="E306"/>
+    </row>
+    <row r="307" spans="3:5">
+      <c r="C307"/>
+      <c r="D307"/>
+      <c r="E307"/>
+    </row>
+    <row r="308" spans="3:5">
+      <c r="C308"/>
+      <c r="D308"/>
+      <c r="E308"/>
+    </row>
+    <row r="309" spans="3:5">
+      <c r="C309"/>
+      <c r="D309"/>
+      <c r="E309"/>
+    </row>
+    <row r="310" spans="3:5">
+      <c r="C310"/>
+      <c r="D310"/>
+      <c r="E310"/>
+    </row>
+    <row r="311" spans="3:5">
+      <c r="C311"/>
+      <c r="D311"/>
+      <c r="E311"/>
+    </row>
+    <row r="312" spans="3:5">
+      <c r="C312"/>
+      <c r="D312"/>
+      <c r="E312"/>
+    </row>
+    <row r="313" spans="3:5">
+      <c r="C313"/>
+      <c r="D313"/>
+      <c r="E313"/>
+    </row>
+    <row r="314" spans="3:5">
+      <c r="C314"/>
+      <c r="D314"/>
+      <c r="E314"/>
+    </row>
+    <row r="315" spans="3:5">
+      <c r="C315"/>
+      <c r="D315"/>
+      <c r="E315"/>
+    </row>
+    <row r="316" spans="3:5">
+      <c r="C316"/>
+      <c r="D316"/>
+      <c r="E316"/>
+    </row>
+    <row r="317" spans="3:5">
+      <c r="C317"/>
+      <c r="D317"/>
+      <c r="E317"/>
+    </row>
+    <row r="318" spans="3:5">
+      <c r="C318"/>
+      <c r="D318"/>
+      <c r="E318"/>
+    </row>
+    <row r="319" spans="3:5">
+      <c r="C319"/>
+      <c r="D319"/>
+      <c r="E319"/>
+    </row>
+    <row r="320" spans="3:5">
+      <c r="C320"/>
+      <c r="D320"/>
+      <c r="E320"/>
+    </row>
+    <row r="321" spans="3:5">
+      <c r="C321"/>
+      <c r="D321"/>
+      <c r="E321"/>
+    </row>
+    <row r="322" spans="3:5">
+      <c r="C322"/>
+      <c r="D322"/>
+      <c r="E322"/>
+    </row>
+    <row r="323" spans="3:5">
+      <c r="C323"/>
+      <c r="D323"/>
+      <c r="E323"/>
+    </row>
+    <row r="324" spans="3:5">
+      <c r="C324"/>
+      <c r="D324"/>
+      <c r="E324"/>
+    </row>
+    <row r="325" spans="3:5">
+      <c r="C325"/>
+      <c r="D325"/>
+      <c r="E325"/>
+    </row>
+    <row r="326" spans="3:5">
+      <c r="C326"/>
+      <c r="D326"/>
+      <c r="E326"/>
+    </row>
+    <row r="327" spans="3:5">
+      <c r="C327"/>
+      <c r="D327"/>
+      <c r="E327"/>
+    </row>
+    <row r="328" spans="3:5">
+      <c r="C328"/>
+      <c r="D328"/>
+      <c r="E328"/>
+    </row>
+    <row r="329" spans="3:5">
+      <c r="C329"/>
+      <c r="D329"/>
+      <c r="E329"/>
+    </row>
+    <row r="330" spans="3:5">
+      <c r="C330"/>
+      <c r="D330"/>
+      <c r="E330"/>
+    </row>
+    <row r="331" spans="3:5">
+      <c r="C331"/>
+      <c r="D331"/>
+      <c r="E331"/>
+    </row>
+    <row r="332" spans="3:5">
+      <c r="C332"/>
+      <c r="D332"/>
+      <c r="E332"/>
+    </row>
+    <row r="333" spans="3:5">
+      <c r="C333"/>
+      <c r="D333"/>
+      <c r="E333"/>
+    </row>
+    <row r="334" spans="3:5">
+      <c r="C334"/>
+      <c r="D334"/>
+      <c r="E334"/>
+    </row>
+    <row r="335" spans="3:5">
+      <c r="C335"/>
+      <c r="D335"/>
+      <c r="E335"/>
+    </row>
+    <row r="336" spans="3:5">
+      <c r="C336"/>
+      <c r="D336"/>
+      <c r="E336"/>
+    </row>
+    <row r="337" spans="3:5">
+      <c r="C337"/>
+      <c r="D337"/>
+      <c r="E337"/>
+    </row>
+    <row r="338" spans="3:5">
+      <c r="C338"/>
+      <c r="D338"/>
+      <c r="E338"/>
+    </row>
+    <row r="339" spans="3:5">
+      <c r="C339"/>
+      <c r="D339"/>
+      <c r="E339"/>
+    </row>
+    <row r="340" spans="3:5">
+      <c r="C340"/>
+      <c r="D340"/>
+      <c r="E340"/>
+    </row>
+    <row r="341" spans="3:5">
+      <c r="C341"/>
+      <c r="D341"/>
+      <c r="E341"/>
+    </row>
+    <row r="342" spans="3:5">
+      <c r="C342"/>
+      <c r="D342"/>
+      <c r="E342"/>
+    </row>
+    <row r="343" spans="3:5">
+      <c r="C343"/>
+      <c r="D343"/>
+      <c r="E343"/>
+    </row>
+    <row r="344" spans="3:5">
+      <c r="C344"/>
+      <c r="D344"/>
+      <c r="E344"/>
+    </row>
+    <row r="345" spans="3:5">
+      <c r="C345"/>
+      <c r="D345"/>
+      <c r="E345"/>
+    </row>
+    <row r="346" spans="3:5">
+      <c r="C346"/>
+      <c r="D346"/>
+      <c r="E346"/>
+    </row>
+    <row r="347" spans="3:5">
+      <c r="C347"/>
+      <c r="D347"/>
+      <c r="E347"/>
+    </row>
+    <row r="348" spans="3:5">
+      <c r="C348"/>
+      <c r="D348"/>
+      <c r="E348"/>
+    </row>
+    <row r="349" spans="3:5">
+      <c r="C349"/>
+      <c r="D349"/>
+      <c r="E349"/>
+    </row>
+    <row r="350" spans="3:5">
+      <c r="C350"/>
+      <c r="D350"/>
+      <c r="E350"/>
+    </row>
+    <row r="351" spans="3:5">
+      <c r="C351"/>
+      <c r="D351"/>
+      <c r="E351"/>
+    </row>
+    <row r="352" spans="3:5">
+      <c r="C352"/>
+      <c r="D352"/>
+      <c r="E352"/>
+    </row>
+    <row r="353" spans="3:5">
+      <c r="C353"/>
+      <c r="D353"/>
+      <c r="E353"/>
+    </row>
+    <row r="354" spans="3:5">
+      <c r="C354"/>
+      <c r="D354"/>
+      <c r="E354"/>
+    </row>
+    <row r="355" spans="3:5">
+      <c r="C355"/>
+      <c r="D355"/>
+      <c r="E355"/>
+    </row>
+    <row r="356" spans="3:5">
+      <c r="C356"/>
+      <c r="D356"/>
+      <c r="E356"/>
+    </row>
+    <row r="357" spans="3:5">
+      <c r="C357"/>
+      <c r="D357"/>
+      <c r="E357"/>
+    </row>
+    <row r="358" spans="3:5">
+      <c r="C358"/>
+      <c r="D358"/>
+      <c r="E358"/>
+    </row>
+    <row r="359" spans="3:5">
+      <c r="C359"/>
+      <c r="D359"/>
+      <c r="E359"/>
+    </row>
+    <row r="360" spans="3:5">
+      <c r="C360"/>
+      <c r="D360"/>
+      <c r="E360"/>
+    </row>
+    <row r="361" spans="3:5">
+      <c r="C361"/>
+      <c r="D361"/>
+      <c r="E361"/>
+    </row>
+    <row r="362" spans="3:5">
+      <c r="C362"/>
+      <c r="D362"/>
+      <c r="E362"/>
+    </row>
+    <row r="363" spans="3:5">
+      <c r="C363"/>
+      <c r="D363"/>
+      <c r="E363"/>
+    </row>
+    <row r="364" spans="3:5">
+      <c r="C364"/>
+      <c r="D364"/>
+      <c r="E364"/>
+    </row>
+    <row r="365" spans="3:5">
+      <c r="C365"/>
+      <c r="D365"/>
+      <c r="E365"/>
+    </row>
+    <row r="366" spans="3:5">
+      <c r="C366"/>
+      <c r="D366"/>
+      <c r="E366"/>
+    </row>
+    <row r="367" spans="3:5">
+      <c r="C367"/>
+      <c r="D367"/>
+      <c r="E367"/>
+    </row>
+    <row r="368" spans="3:5">
+      <c r="C368"/>
+      <c r="D368"/>
+      <c r="E368"/>
+    </row>
+    <row r="369" spans="3:5">
+      <c r="C369"/>
+      <c r="D369"/>
+      <c r="E369"/>
+    </row>
+    <row r="370" spans="3:5">
+      <c r="C370"/>
+      <c r="D370"/>
+      <c r="E370"/>
+    </row>
+    <row r="371" spans="3:5">
+      <c r="C371"/>
+      <c r="D371"/>
+      <c r="E371"/>
+    </row>
+    <row r="372" spans="3:5">
+      <c r="C372"/>
+      <c r="D372"/>
+      <c r="E372"/>
+    </row>
+    <row r="373" spans="3:5">
+      <c r="C373"/>
+      <c r="D373"/>
+      <c r="E373"/>
+    </row>
+    <row r="374" spans="3:5">
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+    </row>
+    <row r="375" spans="3:5">
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+    </row>
+    <row r="376" spans="3:5">
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+    </row>
+    <row r="377" spans="3:5">
+      <c r="C377"/>
+      <c r="D377"/>
+      <c r="E377"/>
+    </row>
+    <row r="378" spans="3:5">
+      <c r="C378"/>
+      <c r="D378"/>
+      <c r="E378"/>
+    </row>
+    <row r="379" spans="3:5">
+      <c r="C379"/>
+      <c r="D379"/>
+      <c r="E379"/>
+    </row>
+    <row r="380" spans="3:5">
+      <c r="C380"/>
+      <c r="D380"/>
+      <c r="E380"/>
+    </row>
+    <row r="381" spans="3:5">
+      <c r="C381"/>
+      <c r="D381"/>
+      <c r="E381"/>
+    </row>
+    <row r="382" spans="3:5">
+      <c r="C382"/>
+      <c r="D382"/>
+      <c r="E382"/>
+    </row>
+    <row r="383" spans="3:5">
+      <c r="C383"/>
+      <c r="D383"/>
+      <c r="E383"/>
+    </row>
+    <row r="384" spans="3:5">
+      <c r="C384"/>
+      <c r="D384"/>
+      <c r="E384"/>
+    </row>
+    <row r="385" spans="3:5">
+      <c r="C385"/>
+      <c r="D385"/>
+      <c r="E385"/>
+    </row>
+    <row r="386" spans="3:5">
+      <c r="C386"/>
+      <c r="D386"/>
+      <c r="E386"/>
+    </row>
+    <row r="387" spans="3:5">
+      <c r="C387"/>
+      <c r="D387"/>
+      <c r="E387"/>
+    </row>
+    <row r="388" spans="3:5">
+      <c r="C388"/>
+      <c r="D388"/>
+      <c r="E388"/>
+    </row>
+    <row r="389" spans="3:5">
+      <c r="C389"/>
+      <c r="D389"/>
+      <c r="E389"/>
+    </row>
+    <row r="390" spans="3:5">
+      <c r="C390"/>
+      <c r="D390"/>
+      <c r="E390"/>
+    </row>
+    <row r="391" spans="3:5">
+      <c r="C391"/>
+      <c r="D391"/>
+      <c r="E391"/>
+    </row>
+    <row r="392" spans="3:5">
+      <c r="C392"/>
+      <c r="D392"/>
+      <c r="E392"/>
+    </row>
+    <row r="393" spans="3:5">
+      <c r="C393"/>
+      <c r="D393"/>
+      <c r="E393"/>
+    </row>
+    <row r="394" spans="3:5">
+      <c r="C394"/>
+      <c r="D394"/>
+      <c r="E394"/>
+    </row>
+    <row r="395" spans="3:5">
+      <c r="C395"/>
+      <c r="D395"/>
+      <c r="E395"/>
+    </row>
+    <row r="396" spans="3:5">
+      <c r="C396"/>
+      <c r="D396"/>
+      <c r="E396"/>
+    </row>
+    <row r="397" spans="3:5">
+      <c r="C397"/>
+      <c r="D397"/>
+      <c r="E397"/>
+    </row>
+    <row r="398" spans="3:5">
+      <c r="C398"/>
+      <c r="D398"/>
+      <c r="E398"/>
+    </row>
+    <row r="399" spans="3:5">
+      <c r="C399"/>
+      <c r="D399"/>
+      <c r="E399"/>
+    </row>
+    <row r="400" spans="3:5">
+      <c r="C400"/>
+      <c r="D400"/>
+      <c r="E400"/>
+    </row>
+    <row r="401" spans="3:5">
+      <c r="C401"/>
+      <c r="D401"/>
+      <c r="E401"/>
+    </row>
+    <row r="402" spans="3:5">
+      <c r="C402"/>
+      <c r="D402"/>
+      <c r="E402"/>
+    </row>
+    <row r="403" spans="3:5">
+      <c r="C403"/>
+      <c r="D403"/>
+      <c r="E403"/>
+    </row>
+    <row r="404" spans="3:5">
+      <c r="C404"/>
+      <c r="D404"/>
+      <c r="E404"/>
+    </row>
+    <row r="405" spans="3:5">
+      <c r="C405"/>
+      <c r="D405"/>
+      <c r="E405"/>
+    </row>
+    <row r="406" spans="3:5">
+      <c r="C406"/>
+      <c r="D406"/>
+      <c r="E406"/>
+    </row>
+    <row r="407" spans="3:5">
+      <c r="C407"/>
+      <c r="D407"/>
+      <c r="E407"/>
+    </row>
+    <row r="408" spans="3:5">
+      <c r="C408"/>
+      <c r="D408"/>
+      <c r="E408"/>
+    </row>
+    <row r="409" spans="3:5">
+      <c r="C409"/>
+      <c r="D409"/>
+      <c r="E409"/>
+    </row>
+    <row r="410" spans="3:5">
+      <c r="C410"/>
+      <c r="D410"/>
+      <c r="E410"/>
+    </row>
+    <row r="411" spans="3:5">
+      <c r="C411"/>
+      <c r="D411"/>
+      <c r="E411"/>
+    </row>
+    <row r="412" spans="3:5">
+      <c r="C412"/>
+      <c r="D412"/>
+      <c r="E412"/>
+    </row>
+    <row r="413" spans="3:5">
+      <c r="C413"/>
+      <c r="D413"/>
+      <c r="E413"/>
+    </row>
+    <row r="414" spans="3:5">
+      <c r="C414"/>
+      <c r="D414"/>
+      <c r="E414"/>
+    </row>
+    <row r="415" spans="3:5">
+      <c r="C415"/>
+      <c r="D415"/>
+      <c r="E415"/>
+    </row>
+    <row r="416" spans="3:5">
+      <c r="C416"/>
+      <c r="D416"/>
+      <c r="E416"/>
+    </row>
+    <row r="417" spans="3:5">
+      <c r="C417"/>
+      <c r="D417"/>
+      <c r="E417"/>
+    </row>
+    <row r="418" spans="3:5">
+      <c r="C418"/>
+      <c r="D418"/>
+      <c r="E418"/>
+    </row>
+    <row r="419" spans="3:5">
+      <c r="C419"/>
+      <c r="D419"/>
+      <c r="E419"/>
+    </row>
+    <row r="420" spans="3:5">
+      <c r="C420"/>
+      <c r="D420"/>
+      <c r="E420"/>
+    </row>
+    <row r="421" spans="3:5">
+      <c r="C421"/>
+      <c r="D421"/>
+      <c r="E421"/>
+    </row>
+    <row r="422" spans="3:5">
+      <c r="C422"/>
+      <c r="D422"/>
+      <c r="E422"/>
+    </row>
+    <row r="423" spans="3:5">
+      <c r="C423"/>
+      <c r="D423"/>
+      <c r="E423"/>
+    </row>
+    <row r="424" spans="3:5">
+      <c r="C424"/>
+      <c r="D424"/>
+      <c r="E424"/>
+    </row>
+    <row r="425" spans="3:5">
+      <c r="C425"/>
+      <c r="D425"/>
+      <c r="E425"/>
+    </row>
+    <row r="426" spans="3:5">
+      <c r="C426"/>
+      <c r="D426"/>
+      <c r="E426"/>
+    </row>
+    <row r="427" spans="3:5">
+      <c r="C427"/>
+      <c r="D427"/>
+      <c r="E427"/>
+    </row>
+    <row r="428" spans="3:5">
+      <c r="C428"/>
+      <c r="D428"/>
+      <c r="E428"/>
+    </row>
+    <row r="429" spans="3:5">
+      <c r="C429"/>
+      <c r="D429"/>
+      <c r="E429"/>
+    </row>
+    <row r="430" spans="3:5">
+      <c r="C430"/>
+      <c r="D430"/>
+      <c r="E430"/>
+    </row>
+    <row r="431" spans="3:5">
+      <c r="C431"/>
+      <c r="D431"/>
+      <c r="E431"/>
+    </row>
+    <row r="432" spans="3:5">
+      <c r="C432"/>
+      <c r="D432"/>
+      <c r="E432"/>
+    </row>
+    <row r="433" spans="3:5">
+      <c r="C433"/>
+      <c r="D433"/>
+      <c r="E433"/>
+    </row>
+    <row r="434" spans="3:5">
+      <c r="C434"/>
+      <c r="D434"/>
+      <c r="E434"/>
+    </row>
+    <row r="435" spans="3:5">
+      <c r="C435"/>
+      <c r="D435"/>
+      <c r="E435"/>
+    </row>
+    <row r="436" spans="3:5">
+      <c r="C436"/>
+      <c r="D436"/>
+      <c r="E436"/>
+    </row>
+    <row r="437" spans="3:5">
+      <c r="C437"/>
+      <c r="D437"/>
+      <c r="E437"/>
+    </row>
+    <row r="438" spans="3:5">
+      <c r="C438"/>
+      <c r="D438"/>
+      <c r="E438"/>
+    </row>
+    <row r="439" spans="3:5">
+      <c r="C439"/>
+      <c r="D439"/>
+      <c r="E439"/>
+    </row>
+    <row r="440" spans="3:5">
+      <c r="C440"/>
+      <c r="D440"/>
+      <c r="E440"/>
+    </row>
+    <row r="441" spans="3:5">
+      <c r="C441"/>
+      <c r="D441"/>
+      <c r="E441"/>
+    </row>
+    <row r="442" spans="3:5">
+      <c r="C442"/>
+      <c r="D442"/>
+      <c r="E442"/>
+    </row>
+    <row r="443" spans="3:5">
+      <c r="C443"/>
+      <c r="D443"/>
+      <c r="E443"/>
+    </row>
+    <row r="444" spans="3:5">
+      <c r="C444"/>
+      <c r="D444"/>
+      <c r="E444"/>
+    </row>
+    <row r="445" spans="3:5">
+      <c r="C445"/>
+      <c r="D445"/>
+      <c r="E445"/>
+    </row>
+    <row r="446" spans="3:5">
+      <c r="C446"/>
+      <c r="D446"/>
+      <c r="E446"/>
+    </row>
+    <row r="447" spans="3:5">
+      <c r="C447"/>
+      <c r="D447"/>
+      <c r="E447"/>
+    </row>
+    <row r="448" spans="3:5">
+      <c r="C448"/>
+      <c r="D448"/>
+      <c r="E448"/>
+    </row>
+    <row r="449" spans="3:5">
+      <c r="C449"/>
+      <c r="D449"/>
+      <c r="E449"/>
+    </row>
+    <row r="450" spans="3:5">
+      <c r="C450"/>
+      <c r="D450"/>
+      <c r="E450"/>
+    </row>
+    <row r="451" spans="3:5">
+      <c r="C451"/>
+      <c r="D451"/>
+      <c r="E451"/>
+    </row>
+    <row r="452" spans="3:5">
+      <c r="C452"/>
+      <c r="D452"/>
+      <c r="E452"/>
+    </row>
+    <row r="453" spans="3:5">
+      <c r="C453"/>
+      <c r="D453"/>
+      <c r="E453"/>
+    </row>
+    <row r="454" spans="3:5">
+      <c r="C454"/>
+      <c r="D454"/>
+      <c r="E454"/>
+    </row>
+    <row r="455" spans="3:5">
+      <c r="C455"/>
+      <c r="D455"/>
+      <c r="E455"/>
+    </row>
+    <row r="456" spans="3:5">
+      <c r="C456"/>
+      <c r="D456"/>
+      <c r="E456"/>
+    </row>
+    <row r="457" spans="3:5">
+      <c r="C457"/>
+      <c r="D457"/>
+      <c r="E457"/>
+    </row>
+    <row r="458" spans="3:5">
+      <c r="C458"/>
+      <c r="D458"/>
+      <c r="E458"/>
+    </row>
+    <row r="459" spans="3:5">
+      <c r="C459"/>
+      <c r="D459"/>
+      <c r="E459"/>
+    </row>
+    <row r="460" spans="3:5">
+      <c r="C460"/>
+      <c r="D460"/>
+      <c r="E460"/>
+    </row>
+    <row r="461" spans="3:5">
+      <c r="C461"/>
+      <c r="D461"/>
+      <c r="E461"/>
+    </row>
+    <row r="462" spans="3:5">
+      <c r="C462"/>
+      <c r="D462"/>
+      <c r="E462"/>
+    </row>
+    <row r="463" spans="3:5">
+      <c r="C463"/>
+      <c r="D463"/>
+      <c r="E463"/>
+    </row>
+    <row r="464" spans="3:5">
+      <c r="C464"/>
+      <c r="D464"/>
+      <c r="E464"/>
+    </row>
+    <row r="465" spans="3:5">
+      <c r="C465"/>
+      <c r="D465"/>
+      <c r="E465"/>
+    </row>
+    <row r="466" spans="3:5">
+      <c r="C466"/>
+      <c r="D466"/>
+      <c r="E466"/>
+    </row>
+    <row r="467" spans="3:5">
+      <c r="C467"/>
+      <c r="D467"/>
+      <c r="E467"/>
+    </row>
+    <row r="468" spans="3:5">
+      <c r="C468"/>
+      <c r="D468"/>
+      <c r="E468"/>
+    </row>
+    <row r="469" spans="3:5">
+      <c r="C469"/>
+      <c r="D469"/>
+      <c r="E469"/>
+    </row>
+    <row r="470" spans="3:5">
+      <c r="C470"/>
+      <c r="D470"/>
+      <c r="E470"/>
+    </row>
+    <row r="471" spans="3:5">
+      <c r="C471"/>
+      <c r="D471"/>
+      <c r="E471"/>
+    </row>
+    <row r="472" spans="3:5">
+      <c r="C472"/>
+      <c r="D472"/>
+      <c r="E472"/>
+    </row>
+    <row r="473" spans="3:5">
+      <c r="C473"/>
+      <c r="D473"/>
+      <c r="E473"/>
+    </row>
+    <row r="474" spans="3:5">
+      <c r="C474"/>
+      <c r="D474"/>
+      <c r="E474"/>
+    </row>
+    <row r="475" spans="3:5">
+      <c r="C475"/>
+      <c r="D475"/>
+      <c r="E475"/>
+    </row>
+    <row r="476" spans="3:5">
+      <c r="C476"/>
+      <c r="D476"/>
+      <c r="E476"/>
+    </row>
+    <row r="477" spans="3:5">
+      <c r="C477"/>
+      <c r="D477"/>
+      <c r="E477"/>
+    </row>
+    <row r="478" spans="3:5">
+      <c r="C478"/>
+      <c r="D478"/>
+      <c r="E478"/>
+    </row>
+    <row r="479" spans="3:5">
+      <c r="C479"/>
+      <c r="D479"/>
+      <c r="E479"/>
+    </row>
+    <row r="480" spans="3:5">
+      <c r="C480"/>
+      <c r="D480"/>
+      <c r="E480"/>
+    </row>
+    <row r="481" spans="3:5">
+      <c r="C481"/>
+      <c r="D481"/>
+      <c r="E481"/>
+    </row>
+    <row r="482" spans="3:5">
+      <c r="C482"/>
+      <c r="D482"/>
+      <c r="E482"/>
+    </row>
+    <row r="483" spans="3:5">
+      <c r="C483"/>
+      <c r="D483"/>
+      <c r="E483"/>
+    </row>
+    <row r="484" spans="3:5">
+      <c r="C484"/>
+      <c r="D484"/>
+      <c r="E484"/>
+    </row>
+    <row r="485" spans="3:5">
+      <c r="C485"/>
+      <c r="D485"/>
+      <c r="E485"/>
+    </row>
+    <row r="486" spans="3:5">
+      <c r="C486"/>
+      <c r="D486"/>
+      <c r="E486"/>
+    </row>
+    <row r="487" spans="3:5">
+      <c r="C487"/>
+      <c r="D487"/>
+      <c r="E487"/>
+    </row>
+    <row r="488" spans="3:5">
+      <c r="C488"/>
+      <c r="D488"/>
+      <c r="E488"/>
+    </row>
+    <row r="489" spans="3:5">
+      <c r="C489"/>
+      <c r="D489"/>
+      <c r="E489"/>
+    </row>
+    <row r="490" spans="3:5">
+      <c r="C490"/>
+      <c r="D490"/>
+      <c r="E490"/>
+    </row>
+    <row r="491" spans="3:5">
+      <c r="C491"/>
+      <c r="D491"/>
+      <c r="E491"/>
+    </row>
+    <row r="492" spans="3:5">
+      <c r="C492"/>
+      <c r="D492"/>
+      <c r="E492"/>
+    </row>
+    <row r="493" spans="3:5">
+      <c r="C493"/>
+      <c r="D493"/>
+      <c r="E493"/>
+    </row>
+    <row r="494" spans="3:5">
+      <c r="C494"/>
+      <c r="D494"/>
+      <c r="E494"/>
+    </row>
+    <row r="495" spans="3:5">
+      <c r="C495"/>
+      <c r="D495"/>
+      <c r="E495"/>
+    </row>
+    <row r="496" spans="3:5">
+      <c r="C496"/>
+      <c r="D496"/>
+      <c r="E496"/>
+    </row>
+    <row r="497" spans="3:5">
+      <c r="C497"/>
+      <c r="D497"/>
+      <c r="E497"/>
+    </row>
+    <row r="498" spans="3:5">
+      <c r="C498"/>
+      <c r="D498"/>
+      <c r="E498"/>
+    </row>
+    <row r="499" spans="3:5">
+      <c r="C499"/>
+      <c r="D499"/>
+      <c r="E499"/>
+    </row>
+    <row r="500" spans="3:5">
+      <c r="C500"/>
+      <c r="D500"/>
+      <c r="E500"/>
+    </row>
+    <row r="501" spans="3:5">
+      <c r="C501"/>
+      <c r="D501"/>
+      <c r="E501"/>
+    </row>
+    <row r="502" spans="3:5">
+      <c r="C502"/>
+      <c r="D502"/>
+      <c r="E502"/>
+    </row>
+    <row r="503" spans="3:5">
+      <c r="C503"/>
+      <c r="D503"/>
+      <c r="E503"/>
+    </row>
+    <row r="504" spans="3:5">
+      <c r="C504"/>
+      <c r="D504"/>
+      <c r="E504"/>
+    </row>
+    <row r="505" spans="3:5">
+      <c r="C505"/>
+      <c r="D505"/>
+      <c r="E505"/>
+    </row>
+    <row r="506" spans="3:5">
+      <c r="C506"/>
+      <c r="D506"/>
+      <c r="E506"/>
+    </row>
+    <row r="507" spans="3:5">
+      <c r="C507"/>
+      <c r="D507"/>
+      <c r="E507"/>
+    </row>
+    <row r="508" spans="3:5">
+      <c r="C508"/>
+      <c r="D508"/>
+      <c r="E508"/>
+    </row>
+    <row r="509" spans="3:5">
+      <c r="C509"/>
+      <c r="D509"/>
+      <c r="E509"/>
+    </row>
+    <row r="510" spans="3:5">
+      <c r="C510"/>
+      <c r="D510"/>
+      <c r="E510"/>
+    </row>
+    <row r="511" spans="3:5">
+      <c r="C511"/>
+      <c r="D511"/>
+      <c r="E511"/>
+    </row>
+    <row r="512" spans="3:5">
+      <c r="C512"/>
+      <c r="D512"/>
+      <c r="E512"/>
+    </row>
+    <row r="513" spans="3:5">
+      <c r="C513"/>
+      <c r="D513"/>
+      <c r="E513"/>
+    </row>
+    <row r="514" spans="3:5">
+      <c r="C514"/>
+      <c r="D514"/>
+      <c r="E514"/>
+    </row>
+    <row r="515" spans="3:5">
+      <c r="C515"/>
+      <c r="D515"/>
+      <c r="E515"/>
+    </row>
+    <row r="516" spans="3:5">
+      <c r="C516"/>
+      <c r="D516"/>
+      <c r="E516"/>
+    </row>
+    <row r="517" spans="3:5">
+      <c r="C517"/>
+      <c r="D517"/>
+      <c r="E517"/>
+    </row>
+    <row r="518" spans="3:5">
+      <c r="C518"/>
+      <c r="D518"/>
+      <c r="E518"/>
+    </row>
+    <row r="519" spans="3:5">
+      <c r="C519"/>
+      <c r="D519"/>
+      <c r="E519"/>
+    </row>
+    <row r="520" spans="3:5">
+      <c r="C520"/>
+      <c r="D520"/>
+      <c r="E520"/>
+    </row>
+    <row r="521" spans="3:5">
+      <c r="C521"/>
+      <c r="D521"/>
+      <c r="E521"/>
+    </row>
+    <row r="522" spans="3:5">
+      <c r="C522"/>
+      <c r="D522"/>
+      <c r="E522"/>
+    </row>
+    <row r="523" spans="3:5">
+      <c r="C523"/>
+      <c r="D523"/>
+      <c r="E523"/>
+    </row>
+    <row r="524" spans="3:5">
+      <c r="C524"/>
+      <c r="D524"/>
+      <c r="E524"/>
+    </row>
+    <row r="525" spans="3:5">
+      <c r="C525"/>
+      <c r="D525"/>
+      <c r="E525"/>
+    </row>
+    <row r="526" spans="3:5">
+      <c r="C526"/>
+      <c r="D526"/>
+      <c r="E526"/>
+    </row>
+    <row r="527" spans="3:5">
+      <c r="C527"/>
+      <c r="D527"/>
+      <c r="E527"/>
+    </row>
+    <row r="528" spans="3:5">
+      <c r="C528"/>
+      <c r="D528"/>
+      <c r="E528"/>
+    </row>
+    <row r="529" spans="3:5">
+      <c r="C529"/>
+      <c r="D529"/>
+      <c r="E529"/>
+    </row>
+    <row r="530" spans="3:5">
+      <c r="C530"/>
+      <c r="D530"/>
+      <c r="E530"/>
+    </row>
+    <row r="531" spans="3:5">
+      <c r="C531"/>
+      <c r="D531"/>
+      <c r="E531"/>
+    </row>
+    <row r="532" spans="3:5">
+      <c r="C532"/>
+      <c r="D532"/>
+      <c r="E532"/>
+    </row>
+    <row r="533" spans="3:5">
+      <c r="C533"/>
+      <c r="D533"/>
+      <c r="E533"/>
+    </row>
+    <row r="534" spans="3:5">
+      <c r="C534"/>
+      <c r="D534"/>
+      <c r="E534"/>
+    </row>
+    <row r="535" spans="3:5">
+      <c r="C535"/>
+      <c r="D535"/>
+      <c r="E535"/>
+    </row>
+    <row r="536" spans="3:5">
+      <c r="C536"/>
+      <c r="D536"/>
+      <c r="E536"/>
+    </row>
+    <row r="537" spans="3:5">
+      <c r="C537"/>
+      <c r="D537"/>
+      <c r="E537"/>
+    </row>
+    <row r="538" spans="3:5">
+      <c r="C538"/>
+      <c r="D538"/>
+      <c r="E538"/>
+    </row>
+    <row r="539" spans="3:5">
+      <c r="C539"/>
+      <c r="D539"/>
+      <c r="E539"/>
+    </row>
+    <row r="540" spans="3:5">
+      <c r="C540"/>
+      <c r="D540"/>
+      <c r="E540"/>
+    </row>
+    <row r="541" spans="3:5">
+      <c r="C541"/>
+      <c r="D541"/>
+      <c r="E541"/>
+    </row>
+    <row r="542" spans="3:5">
+      <c r="C542"/>
+      <c r="D542"/>
+      <c r="E542"/>
+    </row>
+    <row r="543" spans="3:5">
+      <c r="C543"/>
+      <c r="D543"/>
+      <c r="E543"/>
+    </row>
+    <row r="544" spans="3:5">
+      <c r="C544"/>
+      <c r="D544"/>
+      <c r="E544"/>
+    </row>
+    <row r="545" spans="3:5">
+      <c r="C545"/>
+      <c r="D545"/>
+      <c r="E545"/>
+    </row>
+    <row r="546" spans="3:5">
+      <c r="C546"/>
+      <c r="D546"/>
+      <c r="E546"/>
+    </row>
+    <row r="547" spans="3:5">
+      <c r="C547"/>
+      <c r="D547"/>
+      <c r="E547"/>
+    </row>
+    <row r="548" spans="3:5">
+      <c r="C548"/>
+      <c r="D548"/>
+      <c r="E548"/>
+    </row>
+    <row r="549" spans="3:5">
+      <c r="C549"/>
+      <c r="D549"/>
+      <c r="E549"/>
+    </row>
+    <row r="550" spans="3:5">
+      <c r="C550"/>
+      <c r="D550"/>
+      <c r="E550"/>
+    </row>
+    <row r="551" spans="3:5">
+      <c r="C551"/>
+      <c r="D551"/>
+      <c r="E551"/>
+    </row>
+    <row r="552" spans="3:5">
+      <c r="C552"/>
+      <c r="D552"/>
+      <c r="E552"/>
+    </row>
+    <row r="553" spans="3:5">
+      <c r="C553"/>
+      <c r="D553"/>
+      <c r="E553"/>
+    </row>
+    <row r="554" spans="3:5">
+      <c r="C554"/>
+      <c r="D554"/>
+      <c r="E554"/>
+    </row>
+    <row r="555" spans="3:5">
+      <c r="C555"/>
+      <c r="D555"/>
+      <c r="E555"/>
+    </row>
+    <row r="556" spans="3:5">
+      <c r="C556"/>
+      <c r="D556"/>
+      <c r="E556"/>
+    </row>
+    <row r="557" spans="3:5">
+      <c r="C557"/>
+      <c r="D557"/>
+      <c r="E557"/>
+    </row>
+    <row r="558" spans="3:5">
+      <c r="C558"/>
+      <c r="D558"/>
+      <c r="E558"/>
+    </row>
+    <row r="559" spans="3:5">
+      <c r="C559"/>
+      <c r="D559"/>
+      <c r="E559"/>
+    </row>
+    <row r="560" spans="3:5">
+      <c r="C560"/>
+      <c r="D560"/>
+      <c r="E560"/>
+    </row>
+    <row r="561" spans="3:5">
+      <c r="C561"/>
+      <c r="D561"/>
+      <c r="E561"/>
+    </row>
+    <row r="562" spans="3:5">
+      <c r="C562"/>
+      <c r="D562"/>
+      <c r="E562"/>
+    </row>
+    <row r="563" spans="3:5">
+      <c r="C563"/>
+      <c r="D563"/>
+      <c r="E563"/>
+    </row>
+    <row r="564" spans="3:5">
+      <c r="C564"/>
+      <c r="D564"/>
+      <c r="E564"/>
+    </row>
+    <row r="565" spans="3:5">
+      <c r="C565"/>
+      <c r="D565"/>
+      <c r="E565"/>
+    </row>
+    <row r="566" spans="3:5">
+      <c r="C566"/>
+      <c r="D566"/>
+      <c r="E566"/>
+    </row>
+    <row r="567" spans="3:5">
+      <c r="C567"/>
+      <c r="D567"/>
+      <c r="E567"/>
+    </row>
+    <row r="568" spans="3:5">
+      <c r="C568"/>
+      <c r="D568"/>
+      <c r="E568"/>
+    </row>
+    <row r="569" spans="3:5">
+      <c r="C569"/>
+      <c r="D569"/>
+      <c r="E569"/>
+    </row>
+    <row r="570" spans="3:5">
+      <c r="C570"/>
+      <c r="D570"/>
+      <c r="E570"/>
+    </row>
+    <row r="571" spans="3:5">
+      <c r="C571"/>
+      <c r="D571"/>
+      <c r="E571"/>
+    </row>
+    <row r="572" spans="3:5">
+      <c r="C572"/>
+      <c r="D572"/>
+      <c r="E572"/>
+    </row>
+    <row r="573" spans="3:5">
+      <c r="C573"/>
+      <c r="D573"/>
+      <c r="E573"/>
+    </row>
+    <row r="574" spans="3:5">
+      <c r="C574"/>
+      <c r="D574"/>
+      <c r="E574"/>
+    </row>
+    <row r="575" spans="3:5">
+      <c r="C575"/>
+      <c r="D575"/>
+      <c r="E575"/>
+    </row>
+    <row r="576" spans="3:5">
+      <c r="C576"/>
+      <c r="D576"/>
+      <c r="E576"/>
+    </row>
+    <row r="577" spans="3:5">
+      <c r="C577"/>
+      <c r="D577"/>
+      <c r="E577"/>
+    </row>
+    <row r="578" spans="3:5">
+      <c r="C578"/>
+      <c r="D578"/>
+      <c r="E578"/>
+    </row>
+    <row r="579" spans="3:5">
+      <c r="C579"/>
+      <c r="D579"/>
+      <c r="E579"/>
+    </row>
+    <row r="580" spans="3:5">
+      <c r="C580"/>
+      <c r="D580"/>
+      <c r="E580"/>
+    </row>
+    <row r="581" spans="3:5">
+      <c r="C581"/>
+      <c r="D581"/>
+      <c r="E581"/>
+    </row>
+    <row r="582" spans="3:5">
+      <c r="C582"/>
+      <c r="D582"/>
+      <c r="E582"/>
+    </row>
+    <row r="583" spans="3:5">
+      <c r="C583"/>
+      <c r="D583"/>
+      <c r="E583"/>
+    </row>
+    <row r="584" spans="3:5">
+      <c r="C584"/>
+      <c r="D584"/>
+      <c r="E584"/>
+    </row>
+    <row r="585" spans="3:5">
+      <c r="C585"/>
+      <c r="D585"/>
+      <c r="E585"/>
+    </row>
+    <row r="586" spans="3:5">
+      <c r="C586"/>
+      <c r="D586"/>
+      <c r="E586"/>
+    </row>
+    <row r="587" spans="3:5">
+      <c r="C587"/>
+      <c r="D587"/>
+      <c r="E587"/>
+    </row>
+    <row r="588" spans="3:5">
+      <c r="C588"/>
+      <c r="D588"/>
+      <c r="E588"/>
+    </row>
+    <row r="589" spans="3:5">
+      <c r="C589"/>
+      <c r="D589"/>
+      <c r="E589"/>
+    </row>
+    <row r="590" spans="3:5">
+      <c r="C590"/>
+      <c r="D590"/>
+      <c r="E590"/>
+    </row>
+    <row r="591" spans="3:5">
+      <c r="C591"/>
+      <c r="D591"/>
+      <c r="E591"/>
+    </row>
+    <row r="592" spans="3:5">
+      <c r="C592"/>
+      <c r="D592"/>
+      <c r="E592"/>
+    </row>
+    <row r="593" spans="3:5">
+      <c r="C593"/>
+      <c r="D593"/>
+      <c r="E593"/>
+    </row>
+    <row r="594" spans="3:5">
+      <c r="C594"/>
+      <c r="D594"/>
+      <c r="E594"/>
+    </row>
+    <row r="595" spans="3:5">
+      <c r="C595"/>
+      <c r="D595"/>
+      <c r="E595"/>
+    </row>
+    <row r="596" spans="3:5">
+      <c r="C596"/>
+      <c r="D596"/>
+      <c r="E596"/>
+    </row>
+    <row r="597" spans="3:5">
+      <c r="C597"/>
+      <c r="D597"/>
+      <c r="E597"/>
+    </row>
+    <row r="598" spans="3:5">
+      <c r="C598"/>
+      <c r="D598"/>
+      <c r="E598"/>
+    </row>
+    <row r="599" spans="3:5">
+      <c r="C599"/>
+      <c r="D599"/>
+      <c r="E599"/>
+    </row>
+    <row r="600" spans="3:5">
+      <c r="C600"/>
+      <c r="D600"/>
+      <c r="E600"/>
+    </row>
+    <row r="601" spans="3:5">
+      <c r="C601"/>
+      <c r="D601"/>
+      <c r="E601"/>
+    </row>
+    <row r="602" spans="3:5">
+      <c r="C602"/>
+      <c r="D602"/>
+      <c r="E602"/>
+    </row>
+    <row r="603" spans="3:5">
+      <c r="C603"/>
+      <c r="D603"/>
+      <c r="E603"/>
+    </row>
+    <row r="604" spans="3:5">
+      <c r="C604"/>
+      <c r="D604"/>
+      <c r="E604"/>
+    </row>
+    <row r="605" spans="3:5">
+      <c r="C605"/>
+      <c r="D605"/>
+      <c r="E605"/>
+    </row>
+    <row r="606" spans="3:5">
+      <c r="C606"/>
+      <c r="D606"/>
+      <c r="E606"/>
+    </row>
+    <row r="607" spans="3:5">
+      <c r="C607"/>
+      <c r="D607"/>
+      <c r="E607"/>
+    </row>
+    <row r="608" spans="3:5">
+      <c r="C608"/>
+      <c r="D608"/>
+      <c r="E608"/>
+    </row>
+    <row r="609" spans="3:5">
+      <c r="C609"/>
+      <c r="D609"/>
+      <c r="E609"/>
+    </row>
+    <row r="610" spans="3:5">
+      <c r="C610"/>
+      <c r="D610"/>
+      <c r="E610"/>
+    </row>
+    <row r="611" spans="3:5">
+      <c r="C611"/>
+      <c r="D611"/>
+      <c r="E611"/>
+    </row>
+    <row r="612" spans="3:5">
+      <c r="C612"/>
+      <c r="D612"/>
+      <c r="E612"/>
+    </row>
+    <row r="613" spans="3:5">
+      <c r="C613"/>
+      <c r="D613"/>
+      <c r="E613"/>
+    </row>
+    <row r="614" spans="3:5">
+      <c r="C614"/>
+      <c r="D614"/>
+      <c r="E614"/>
+    </row>
+    <row r="615" spans="3:5">
+      <c r="C615"/>
+      <c r="D615"/>
+      <c r="E615"/>
+    </row>
+    <row r="616" spans="3:5">
+      <c r="C616"/>
+      <c r="D616"/>
+      <c r="E616"/>
+    </row>
+    <row r="617" spans="3:5">
+      <c r="C617"/>
+      <c r="D617"/>
+      <c r="E617"/>
+    </row>
+    <row r="618" spans="3:5">
+      <c r="C618"/>
+      <c r="D618"/>
+      <c r="E618"/>
+    </row>
+    <row r="619" spans="3:5">
+      <c r="C619"/>
+      <c r="D619"/>
+      <c r="E619"/>
+    </row>
+    <row r="620" spans="3:5">
+      <c r="C620"/>
+      <c r="D620"/>
+      <c r="E620"/>
+    </row>
+    <row r="621" spans="3:5">
+      <c r="C621"/>
+      <c r="D621"/>
+      <c r="E621"/>
+    </row>
+    <row r="622" spans="3:5">
+      <c r="C622"/>
+      <c r="D622"/>
+      <c r="E622"/>
+    </row>
+    <row r="623" spans="3:5">
+      <c r="C623"/>
+      <c r="D623"/>
+      <c r="E623"/>
+    </row>
+    <row r="624" spans="3:5">
+      <c r="C624"/>
+      <c r="D624"/>
+      <c r="E624"/>
+    </row>
+    <row r="625" spans="3:5">
+      <c r="C625"/>
+      <c r="D625"/>
+      <c r="E625"/>
+    </row>
+    <row r="626" spans="3:5">
+      <c r="C626"/>
+      <c r="D626"/>
+      <c r="E626"/>
+    </row>
+    <row r="627" spans="3:5">
+      <c r="C627"/>
+      <c r="D627"/>
+      <c r="E627"/>
+    </row>
+    <row r="628" spans="3:5">
+      <c r="C628"/>
+      <c r="D628"/>
+      <c r="E628"/>
+    </row>
+    <row r="629" spans="3:5">
+      <c r="C629"/>
+      <c r="D629"/>
+      <c r="E629"/>
+    </row>
+    <row r="630" spans="3:5">
+      <c r="C630"/>
+      <c r="D630"/>
+      <c r="E630"/>
+    </row>
+    <row r="631" spans="3:5">
+      <c r="C631"/>
+      <c r="D631"/>
+      <c r="E631"/>
+    </row>
+    <row r="632" spans="3:5">
+      <c r="C632"/>
+      <c r="D632"/>
+      <c r="E632"/>
+    </row>
+    <row r="633" spans="3:5">
+      <c r="C633"/>
+      <c r="D633"/>
+      <c r="E633"/>
+    </row>
+    <row r="634" spans="3:5">
+      <c r="C634"/>
+      <c r="D634"/>
+      <c r="E634"/>
+    </row>
+    <row r="635" spans="3:5">
+      <c r="C635"/>
+      <c r="D635"/>
+      <c r="E635"/>
+    </row>
+    <row r="636" spans="3:5">
+      <c r="C636"/>
+      <c r="D636"/>
+      <c r="E636"/>
+    </row>
+    <row r="637" spans="3:5">
+      <c r="C637"/>
+      <c r="D637"/>
+      <c r="E637"/>
+    </row>
+    <row r="638" spans="3:5">
+      <c r="C638"/>
+      <c r="D638"/>
+      <c r="E638"/>
+    </row>
+    <row r="639" spans="3:5">
+      <c r="C639"/>
+      <c r="D639"/>
+      <c r="E639"/>
+    </row>
+    <row r="640" spans="3:5">
+      <c r="C640"/>
+      <c r="D640"/>
+      <c r="E640"/>
+    </row>
+    <row r="641" spans="3:5">
+      <c r="C641"/>
+      <c r="D641"/>
+      <c r="E641"/>
+    </row>
+    <row r="642" spans="3:5">
+      <c r="C642"/>
+      <c r="D642"/>
+      <c r="E642"/>
+    </row>
+    <row r="643" spans="3:5">
+      <c r="C643"/>
+      <c r="D643"/>
+      <c r="E643"/>
+    </row>
+    <row r="644" spans="3:5">
+      <c r="C644"/>
+      <c r="D644"/>
+      <c r="E644"/>
+    </row>
+    <row r="645" spans="3:5">
+      <c r="C645"/>
+      <c r="D645"/>
+      <c r="E645"/>
+    </row>
+    <row r="646" spans="3:5">
+      <c r="C646"/>
+      <c r="D646"/>
+      <c r="E646"/>
+    </row>
+    <row r="647" spans="3:5">
+      <c r="C647"/>
+      <c r="D647"/>
+      <c r="E647"/>
+    </row>
+    <row r="648" spans="3:5">
+      <c r="C648"/>
+      <c r="D648"/>
+      <c r="E648"/>
+    </row>
+    <row r="649" spans="3:5">
+      <c r="C649"/>
+      <c r="D649"/>
+      <c r="E649"/>
+    </row>
+    <row r="650" spans="3:5">
+      <c r="C650"/>
+      <c r="D650"/>
+      <c r="E650"/>
+    </row>
+    <row r="651" spans="3:5">
+      <c r="C651"/>
+      <c r="D651"/>
+      <c r="E651"/>
+    </row>
+    <row r="652" spans="3:5">
+      <c r="C652"/>
+      <c r="D652"/>
+      <c r="E652"/>
+    </row>
+    <row r="653" spans="3:5">
+      <c r="C653"/>
+      <c r="D653"/>
+      <c r="E653"/>
+    </row>
+    <row r="654" spans="3:5">
+      <c r="C654"/>
+      <c r="D654"/>
+      <c r="E654"/>
+    </row>
+    <row r="655" spans="3:5">
+      <c r="C655"/>
+      <c r="D655"/>
+      <c r="E655"/>
+    </row>
+    <row r="656" spans="3:5">
+      <c r="C656"/>
+      <c r="D656"/>
+      <c r="E656"/>
+    </row>
+    <row r="657" spans="3:5">
+      <c r="C657"/>
+      <c r="D657"/>
+      <c r="E657"/>
+    </row>
+    <row r="658" spans="3:5">
+      <c r="C658"/>
+      <c r="D658"/>
+      <c r="E658"/>
+    </row>
+    <row r="659" spans="3:5">
+      <c r="C659"/>
+      <c r="D659"/>
+      <c r="E659"/>
+    </row>
+    <row r="660" spans="3:5">
+      <c r="C660"/>
+      <c r="D660"/>
+      <c r="E660"/>
+    </row>
+    <row r="661" spans="3:5">
+      <c r="C661"/>
+      <c r="D661"/>
+      <c r="E661"/>
+    </row>
+    <row r="662" spans="3:5">
+      <c r="C662"/>
+      <c r="D662"/>
+      <c r="E662"/>
+    </row>
+    <row r="663" spans="3:5">
+      <c r="C663"/>
+      <c r="D663"/>
+      <c r="E663"/>
+    </row>
+    <row r="664" spans="3:5">
+      <c r="C664"/>
+      <c r="D664"/>
+      <c r="E664"/>
+    </row>
+    <row r="665" spans="3:5">
+      <c r="C665"/>
+      <c r="D665"/>
+      <c r="E665"/>
+    </row>
+    <row r="666" spans="3:5">
+      <c r="C666"/>
+      <c r="D666"/>
+      <c r="E666"/>
+    </row>
+    <row r="667" spans="3:5">
+      <c r="C667"/>
+      <c r="D667"/>
+      <c r="E667"/>
+    </row>
+    <row r="668" spans="3:5">
+      <c r="C668"/>
+      <c r="D668"/>
+      <c r="E668"/>
+    </row>
+    <row r="669" spans="3:5">
+      <c r="C669"/>
+      <c r="D669"/>
+      <c r="E669"/>
+    </row>
+    <row r="670" spans="3:5">
+      <c r="C670"/>
+      <c r="D670"/>
+      <c r="E670"/>
+    </row>
+    <row r="671" spans="3:5">
+      <c r="C671"/>
+      <c r="D671"/>
+      <c r="E671"/>
+    </row>
+    <row r="672" spans="3:5">
+      <c r="C672"/>
+      <c r="D672"/>
+      <c r="E672"/>
+    </row>
+    <row r="673" spans="3:5">
+      <c r="C673"/>
+      <c r="D673"/>
+      <c r="E673"/>
+    </row>
+    <row r="674" spans="3:5">
+      <c r="C674"/>
+      <c r="D674"/>
+      <c r="E674"/>
+    </row>
+    <row r="675" spans="3:5">
+      <c r="C675"/>
+      <c r="D675"/>
+      <c r="E675"/>
+    </row>
+    <row r="676" spans="3:5">
+      <c r="C676"/>
+      <c r="D676"/>
+      <c r="E676"/>
+    </row>
+    <row r="677" spans="3:5">
+      <c r="C677"/>
+      <c r="D677"/>
+      <c r="E677"/>
+    </row>
+    <row r="678" spans="3:5">
+      <c r="C678"/>
+      <c r="D678"/>
+      <c r="E678"/>
+    </row>
+    <row r="679" spans="3:5">
+      <c r="C679"/>
+      <c r="D679"/>
+      <c r="E679"/>
+    </row>
+    <row r="680" spans="3:5">
+      <c r="C680"/>
+      <c r="D680"/>
+      <c r="E680"/>
+    </row>
+    <row r="681" spans="3:5">
+      <c r="C681"/>
+      <c r="D681"/>
+      <c r="E681"/>
+    </row>
+    <row r="682" spans="3:5">
+      <c r="C682"/>
+      <c r="D682"/>
+      <c r="E682"/>
+    </row>
+    <row r="683" spans="3:5">
+      <c r="C683"/>
+      <c r="D683"/>
+      <c r="E683"/>
+    </row>
+    <row r="684" spans="3:5">
+      <c r="C684"/>
+      <c r="D684"/>
+      <c r="E684"/>
+    </row>
+    <row r="685" spans="3:5">
+      <c r="C685"/>
+      <c r="D685"/>
+      <c r="E685"/>
+    </row>
+    <row r="686" spans="3:5">
+      <c r="C686"/>
+      <c r="D686"/>
+      <c r="E686"/>
+    </row>
+    <row r="687" spans="3:5">
+      <c r="C687"/>
+      <c r="D687"/>
+      <c r="E687"/>
+    </row>
+    <row r="688" spans="3:5">
+      <c r="C688"/>
+      <c r="D688"/>
+      <c r="E688"/>
+    </row>
+    <row r="689" spans="3:5">
+      <c r="C689"/>
+      <c r="D689"/>
+      <c r="E689"/>
+    </row>
+    <row r="690" spans="3:5">
+      <c r="C690"/>
+      <c r="D690"/>
+      <c r="E690"/>
+    </row>
+    <row r="691" spans="3:5">
+      <c r="C691"/>
+      <c r="D691"/>
+      <c r="E691"/>
+    </row>
+    <row r="692" spans="3:5">
+      <c r="C692"/>
+      <c r="D692"/>
+      <c r="E692"/>
+    </row>
+    <row r="693" spans="3:5">
+      <c r="C693"/>
+      <c r="D693"/>
+      <c r="E693"/>
+    </row>
+    <row r="694" spans="3:5">
+      <c r="C694"/>
+      <c r="D694"/>
+      <c r="E694"/>
+    </row>
+    <row r="695" spans="3:5">
+      <c r="C695"/>
+      <c r="D695"/>
+      <c r="E695"/>
+    </row>
+    <row r="696" spans="3:5">
+      <c r="C696"/>
+      <c r="D696"/>
+      <c r="E696"/>
+    </row>
+    <row r="697" spans="3:5">
+      <c r="C697"/>
+      <c r="D697"/>
+      <c r="E697"/>
+    </row>
+    <row r="698" spans="3:5">
+      <c r="C698"/>
+      <c r="D698"/>
+      <c r="E698"/>
+    </row>
+    <row r="699" spans="3:5">
+      <c r="C699"/>
+      <c r="D699"/>
+      <c r="E699"/>
+    </row>
+    <row r="700" spans="3:5">
+      <c r="C700"/>
+      <c r="D700"/>
+      <c r="E700"/>
+    </row>
+    <row r="701" spans="3:5">
+      <c r="C701"/>
+      <c r="D701"/>
+      <c r="E701"/>
+    </row>
+    <row r="702" spans="3:5">
+      <c r="C702"/>
+      <c r="D702"/>
+      <c r="E702"/>
+    </row>
+    <row r="703" spans="3:5">
+      <c r="C703"/>
+      <c r="D703"/>
+      <c r="E703"/>
+    </row>
+    <row r="704" spans="3:5">
+      <c r="C704"/>
+      <c r="D704"/>
+      <c r="E704"/>
+    </row>
+    <row r="705" spans="3:5">
+      <c r="C705"/>
+      <c r="D705"/>
+      <c r="E705"/>
+    </row>
+    <row r="706" spans="3:5">
+      <c r="C706"/>
+      <c r="D706"/>
+      <c r="E706"/>
+    </row>
+    <row r="707" spans="3:5">
+      <c r="C707"/>
+      <c r="D707"/>
+      <c r="E707"/>
+    </row>
+    <row r="708" spans="3:5">
+      <c r="C708"/>
+      <c r="D708"/>
+      <c r="E708"/>
+    </row>
+    <row r="709" spans="3:5">
+      <c r="C709"/>
+      <c r="D709"/>
+      <c r="E709"/>
+    </row>
+    <row r="710" spans="3:5">
+      <c r="C710"/>
+      <c r="D710"/>
+      <c r="E710"/>
+    </row>
+    <row r="711" spans="3:5">
+      <c r="C711"/>
+      <c r="D711"/>
+      <c r="E711"/>
+    </row>
+    <row r="712" spans="3:5">
+      <c r="C712"/>
+      <c r="D712"/>
+      <c r="E712"/>
+    </row>
+    <row r="713" spans="3:5">
+      <c r="C713"/>
+      <c r="D713"/>
+      <c r="E713"/>
+    </row>
+    <row r="714" spans="3:5">
+      <c r="C714"/>
+      <c r="D714"/>
+      <c r="E714"/>
+    </row>
+    <row r="715" spans="3:5">
+      <c r="C715"/>
+      <c r="D715"/>
+      <c r="E715"/>
+    </row>
+    <row r="716" spans="3:5">
+      <c r="C716"/>
+      <c r="D716"/>
+      <c r="E716"/>
+    </row>
+    <row r="717" spans="3:5">
+      <c r="C717"/>
+      <c r="D717"/>
+      <c r="E717"/>
+    </row>
+    <row r="718" spans="3:5">
+      <c r="C718"/>
+      <c r="D718"/>
+      <c r="E718"/>
+    </row>
+    <row r="719" spans="3:5">
+      <c r="C719"/>
+      <c r="D719"/>
+      <c r="E719"/>
+    </row>
+    <row r="720" spans="3:5">
+      <c r="C720"/>
+      <c r="D720"/>
+      <c r="E720"/>
+    </row>
+    <row r="721" spans="3:5">
+      <c r="C721"/>
+      <c r="D721"/>
+      <c r="E721"/>
+    </row>
+    <row r="722" spans="3:5">
+      <c r="C722"/>
+      <c r="D722"/>
+      <c r="E722"/>
+    </row>
+    <row r="723" spans="3:5">
+      <c r="C723"/>
+      <c r="D723"/>
+      <c r="E723"/>
+    </row>
+    <row r="724" spans="3:5">
+      <c r="C724"/>
+      <c r="D724"/>
+      <c r="E724"/>
+    </row>
+    <row r="725" spans="3:5">
+      <c r="C725"/>
+      <c r="D725"/>
+      <c r="E725"/>
+    </row>
+    <row r="726" spans="3:5">
+      <c r="C726"/>
+      <c r="D726"/>
+      <c r="E726"/>
+    </row>
+    <row r="727" spans="3:5">
+      <c r="C727"/>
+      <c r="D727"/>
+      <c r="E727"/>
+    </row>
+    <row r="728" spans="3:5">
+      <c r="C728"/>
+      <c r="D728"/>
+      <c r="E728"/>
+    </row>
+    <row r="729" spans="3:5">
+      <c r="C729"/>
+      <c r="D729"/>
+      <c r="E729"/>
+    </row>
+    <row r="730" spans="3:5">
+      <c r="C730"/>
+      <c r="D730"/>
+      <c r="E730"/>
+    </row>
+    <row r="731" spans="3:5">
+      <c r="C731"/>
+      <c r="D731"/>
+      <c r="E731"/>
+    </row>
+    <row r="732" spans="3:5">
+      <c r="C732"/>
+      <c r="D732"/>
+      <c r="E732"/>
+    </row>
+    <row r="733" spans="3:5">
+      <c r="C733"/>
+      <c r="D733"/>
+      <c r="E733"/>
+    </row>
+    <row r="734" spans="3:5">
+      <c r="C734"/>
+      <c r="D734"/>
+      <c r="E734"/>
+    </row>
+    <row r="735" spans="3:5">
+      <c r="C735"/>
+      <c r="D735"/>
+      <c r="E735"/>
+    </row>
+    <row r="736" spans="3:5">
+      <c r="C736"/>
+      <c r="D736"/>
+      <c r="E736"/>
+    </row>
+    <row r="737" spans="3:5">
+      <c r="C737"/>
+      <c r="D737"/>
+      <c r="E737"/>
+    </row>
+    <row r="738" spans="3:5">
+      <c r="C738"/>
+      <c r="D738"/>
+      <c r="E738"/>
+    </row>
+    <row r="739" spans="3:5">
+      <c r="C739"/>
+      <c r="D739"/>
+      <c r="E739"/>
+    </row>
+    <row r="740" spans="3:5">
+      <c r="C740"/>
+      <c r="D740"/>
+      <c r="E740"/>
+    </row>
+    <row r="741" spans="3:5">
+      <c r="C741"/>
+      <c r="D741"/>
+      <c r="E741"/>
+    </row>
+    <row r="742" spans="3:5">
+      <c r="C742"/>
+      <c r="D742"/>
+      <c r="E742"/>
+    </row>
+    <row r="743" spans="3:5">
+      <c r="C743"/>
+      <c r="D743"/>
+      <c r="E743"/>
+    </row>
+    <row r="744" spans="3:5">
+      <c r="C744"/>
+      <c r="D744"/>
+      <c r="E744"/>
+    </row>
+    <row r="745" spans="3:5">
+      <c r="C745"/>
+      <c r="D745"/>
+      <c r="E745"/>
+    </row>
+    <row r="746" spans="3:5">
+      <c r="C746"/>
+      <c r="D746"/>
+      <c r="E746"/>
+    </row>
+    <row r="747" spans="3:5">
+      <c r="C747"/>
+      <c r="D747"/>
+      <c r="E747"/>
+    </row>
+    <row r="748" spans="3:5">
+      <c r="C748"/>
+      <c r="D748"/>
+      <c r="E748"/>
+    </row>
+    <row r="749" spans="3:5">
+      <c r="C749"/>
+      <c r="D749"/>
+      <c r="E749"/>
+    </row>
+    <row r="750" spans="3:5">
+      <c r="C750"/>
+      <c r="D750"/>
+      <c r="E750"/>
+    </row>
+    <row r="751" spans="3:5">
+      <c r="C751"/>
+      <c r="D751"/>
+      <c r="E751"/>
+    </row>
+    <row r="752" spans="3:5">
+      <c r="C752"/>
+      <c r="D752"/>
+      <c r="E752"/>
+    </row>
+    <row r="753" spans="3:5">
+      <c r="C753"/>
+      <c r="D753"/>
+      <c r="E753"/>
+    </row>
+    <row r="754" spans="3:5">
+      <c r="C754"/>
+      <c r="D754"/>
+      <c r="E754"/>
+    </row>
+    <row r="755" spans="3:5">
+      <c r="C755"/>
+      <c r="D755"/>
+      <c r="E755"/>
+    </row>
+    <row r="756" spans="3:5">
+      <c r="C756"/>
+      <c r="D756"/>
+      <c r="E756"/>
+    </row>
+    <row r="757" spans="3:5">
+      <c r="C757"/>
+      <c r="D757"/>
+      <c r="E757"/>
+    </row>
+    <row r="758" spans="3:5">
+      <c r="C758"/>
+      <c r="D758"/>
+      <c r="E758"/>
+    </row>
+    <row r="759" spans="3:5">
+      <c r="C759"/>
+      <c r="D759"/>
+      <c r="E759"/>
+    </row>
+    <row r="760" spans="3:5">
+      <c r="C760"/>
+      <c r="D760"/>
+      <c r="E760"/>
+    </row>
+    <row r="761" spans="3:5">
+      <c r="C761"/>
+      <c r="D761"/>
+      <c r="E761"/>
+    </row>
+    <row r="762" spans="3:5">
+      <c r="C762"/>
+      <c r="D762"/>
+      <c r="E762"/>
+    </row>
+    <row r="763" spans="3:5">
+      <c r="C763"/>
+      <c r="D763"/>
+      <c r="E763"/>
+    </row>
+    <row r="764" spans="3:5">
+      <c r="C764"/>
+      <c r="D764"/>
+      <c r="E764"/>
+    </row>
+    <row r="765" spans="3:5">
+      <c r="C765"/>
+      <c r="D765"/>
+      <c r="E765"/>
+    </row>
+    <row r="766" spans="3:5">
+      <c r="C766"/>
+      <c r="D766"/>
+      <c r="E766"/>
+    </row>
+    <row r="767" spans="3:5">
+      <c r="C767"/>
+      <c r="D767"/>
+      <c r="E767"/>
+    </row>
+    <row r="768" spans="3:5">
+      <c r="C768"/>
+      <c r="D768"/>
+      <c r="E768"/>
+    </row>
+    <row r="769" spans="3:5">
+      <c r="C769"/>
+      <c r="D769"/>
+      <c r="E769"/>
+    </row>
+    <row r="770" spans="3:5">
+      <c r="C770"/>
+      <c r="D770"/>
+      <c r="E770"/>
+    </row>
+    <row r="771" spans="3:5">
+      <c r="C771"/>
+      <c r="D771"/>
+      <c r="E771"/>
+    </row>
+    <row r="772" spans="3:5">
+      <c r="C772"/>
+      <c r="D772"/>
+      <c r="E772"/>
+    </row>
+    <row r="773" spans="3:5">
+      <c r="C773"/>
+      <c r="D773"/>
+      <c r="E773"/>
+    </row>
+    <row r="774" spans="3:5">
+      <c r="C774"/>
+      <c r="D774"/>
+      <c r="E774"/>
+    </row>
+    <row r="775" spans="3:5">
+      <c r="C775"/>
+      <c r="D775"/>
+      <c r="E775"/>
+    </row>
+    <row r="776" spans="3:5">
+      <c r="C776"/>
+      <c r="D776"/>
+      <c r="E776"/>
+    </row>
+    <row r="777" spans="3:5">
+      <c r="C777"/>
+      <c r="D777"/>
+      <c r="E777"/>
+    </row>
+    <row r="778" spans="3:5">
+      <c r="C778"/>
+      <c r="D778"/>
+      <c r="E778"/>
+    </row>
+    <row r="779" spans="3:5">
+      <c r="C779"/>
+      <c r="D779"/>
+      <c r="E779"/>
+    </row>
+    <row r="780" spans="3:5">
+      <c r="C780"/>
+      <c r="D780"/>
+      <c r="E780"/>
+    </row>
+    <row r="781" spans="3:5">
+      <c r="C781"/>
+      <c r="D781"/>
+      <c r="E781"/>
+    </row>
+    <row r="782" spans="3:5">
+      <c r="C782"/>
+      <c r="D782"/>
+      <c r="E782"/>
+    </row>
+    <row r="783" spans="3:5">
+      <c r="C783"/>
+      <c r="D783"/>
+      <c r="E783"/>
+    </row>
+    <row r="784" spans="3:5">
+      <c r="C784"/>
+      <c r="D784"/>
+      <c r="E784"/>
+    </row>
+    <row r="785" spans="3:5">
+      <c r="C785"/>
+      <c r="D785"/>
+      <c r="E785"/>
+    </row>
+    <row r="786" spans="3:5">
+      <c r="C786"/>
+      <c r="D786"/>
+      <c r="E786"/>
+    </row>
+    <row r="787" spans="3:5">
+      <c r="C787"/>
+      <c r="D787"/>
+      <c r="E787"/>
+    </row>
+    <row r="788" spans="3:5">
+      <c r="C788"/>
+      <c r="D788"/>
+      <c r="E788"/>
+    </row>
+    <row r="789" spans="3:5">
+      <c r="C789"/>
+      <c r="D789"/>
+      <c r="E789"/>
+    </row>
+    <row r="790" spans="3:5">
+      <c r="C790"/>
+      <c r="D790"/>
+      <c r="E790"/>
+    </row>
+    <row r="791" spans="3:5">
+      <c r="C791"/>
+      <c r="D791"/>
+      <c r="E791"/>
+    </row>
+    <row r="792" spans="3:5">
+      <c r="C792"/>
+      <c r="D792"/>
+      <c r="E792"/>
+    </row>
+    <row r="793" spans="3:5">
+      <c r="C793"/>
+      <c r="D793"/>
+      <c r="E793"/>
+    </row>
+    <row r="794" spans="3:5">
+      <c r="C794"/>
+      <c r="D794"/>
+      <c r="E794"/>
+    </row>
+    <row r="795" spans="3:5">
+      <c r="C795"/>
+      <c r="D795"/>
+      <c r="E795"/>
+    </row>
+    <row r="796" spans="3:5">
+      <c r="C796"/>
+      <c r="D796"/>
+      <c r="E796"/>
+    </row>
+    <row r="797" spans="3:5">
+      <c r="C797"/>
+      <c r="D797"/>
+      <c r="E797"/>
+    </row>
+    <row r="798" spans="3:5">
+      <c r="C798"/>
+      <c r="D798"/>
+      <c r="E798"/>
+    </row>
+    <row r="799" spans="3:5">
+      <c r="C799"/>
+      <c r="D799"/>
+      <c r="E799"/>
+    </row>
+    <row r="800" spans="3:5">
+      <c r="C800"/>
+      <c r="D800"/>
+      <c r="E800"/>
+    </row>
+    <row r="801" spans="3:5">
+      <c r="C801"/>
+      <c r="D801"/>
+      <c r="E801"/>
+    </row>
+    <row r="802" spans="3:5">
+      <c r="C802"/>
+      <c r="D802"/>
+      <c r="E802"/>
+    </row>
+    <row r="803" spans="3:5">
+      <c r="C803"/>
+      <c r="D803"/>
+      <c r="E803"/>
+    </row>
+    <row r="804" spans="3:5">
+      <c r="C804"/>
+      <c r="D804"/>
+      <c r="E804"/>
+    </row>
+    <row r="805" spans="3:5">
+      <c r="C805"/>
+      <c r="D805"/>
+      <c r="E805"/>
+    </row>
+    <row r="806" spans="3:5">
+      <c r="C806"/>
+      <c r="D806"/>
+      <c r="E806"/>
+    </row>
+    <row r="807" spans="3:5">
+      <c r="C807"/>
+      <c r="D807"/>
+      <c r="E807"/>
+    </row>
+    <row r="808" spans="3:5">
+      <c r="C808"/>
+      <c r="D808"/>
+      <c r="E808"/>
+    </row>
+    <row r="809" spans="3:5">
+      <c r="C809"/>
+      <c r="D809"/>
+      <c r="E809"/>
+    </row>
+    <row r="810" spans="3:5">
+      <c r="C810"/>
+      <c r="D810"/>
+      <c r="E810"/>
+    </row>
+    <row r="811" spans="3:5">
+      <c r="C811"/>
+      <c r="D811"/>
+      <c r="E811"/>
+    </row>
+    <row r="812" spans="3:5">
+      <c r="C812"/>
+      <c r="D812"/>
+      <c r="E812"/>
+    </row>
+    <row r="813" spans="3:5">
+      <c r="C813"/>
+      <c r="D813"/>
+      <c r="E813"/>
+    </row>
+    <row r="814" spans="3:5">
+      <c r="C814"/>
+      <c r="D814"/>
+      <c r="E814"/>
+    </row>
+    <row r="815" spans="3:5">
+      <c r="C815"/>
+      <c r="D815"/>
+      <c r="E815"/>
+    </row>
+    <row r="816" spans="3:5">
+      <c r="C816"/>
+      <c r="D816"/>
+      <c r="E816"/>
+    </row>
+    <row r="817" spans="3:5">
+      <c r="C817"/>
+      <c r="D817"/>
+      <c r="E817"/>
+    </row>
+    <row r="818" spans="3:5">
+      <c r="C818"/>
+      <c r="D818"/>
+      <c r="E818"/>
+    </row>
+    <row r="819" spans="3:5">
+      <c r="C819"/>
+      <c r="D819"/>
+      <c r="E819"/>
+    </row>
+    <row r="820" spans="3:5">
+      <c r="C820"/>
+      <c r="D820"/>
+      <c r="E820"/>
+    </row>
+    <row r="821" spans="3:5">
+      <c r="C821"/>
+      <c r="D821"/>
+      <c r="E821"/>
+    </row>
+    <row r="822" spans="3:5">
+      <c r="C822"/>
+      <c r="D822"/>
+      <c r="E822"/>
+    </row>
+    <row r="823" spans="3:5">
+      <c r="C823"/>
+      <c r="D823"/>
+      <c r="E823"/>
+    </row>
+    <row r="824" spans="3:5">
+      <c r="C824"/>
+      <c r="D824"/>
+      <c r="E824"/>
+    </row>
+    <row r="825" spans="3:5">
+      <c r="C825"/>
+      <c r="D825"/>
+      <c r="E825"/>
+    </row>
+    <row r="826" spans="3:5">
+      <c r="C826"/>
+      <c r="D826"/>
+      <c r="E826"/>
+    </row>
+    <row r="827" spans="3:5">
+      <c r="C827"/>
+      <c r="D827"/>
+      <c r="E827"/>
+    </row>
+    <row r="828" spans="3:5">
+      <c r="C828"/>
+      <c r="D828"/>
+      <c r="E828"/>
+    </row>
+    <row r="829" spans="3:5">
+      <c r="C829"/>
+      <c r="D829"/>
+      <c r="E829"/>
+    </row>
+    <row r="830" spans="3:5">
+      <c r="C830"/>
+      <c r="D830"/>
+      <c r="E830"/>
+    </row>
+    <row r="831" spans="3:5">
+      <c r="C831"/>
+      <c r="D831"/>
+      <c r="E831"/>
+    </row>
+    <row r="832" spans="3:5">
+      <c r="C832"/>
+      <c r="D832"/>
+      <c r="E832"/>
+    </row>
+    <row r="833" spans="3:5">
+      <c r="C833"/>
+      <c r="D833"/>
+      <c r="E833"/>
+    </row>
+    <row r="834" spans="3:5">
+      <c r="C834"/>
+      <c r="D834"/>
+      <c r="E834"/>
+    </row>
+    <row r="835" spans="3:5">
+      <c r="C835"/>
+      <c r="D835"/>
+      <c r="E835"/>
+    </row>
+    <row r="836" spans="3:5">
+      <c r="C836"/>
+      <c r="D836"/>
+      <c r="E836"/>
+    </row>
+    <row r="837" spans="3:5">
+      <c r="C837"/>
+      <c r="D837"/>
+      <c r="E837"/>
+    </row>
+    <row r="838" spans="3:5">
+      <c r="C838"/>
+      <c r="D838"/>
+      <c r="E838"/>
+    </row>
+    <row r="839" spans="3:5">
+      <c r="C839"/>
+      <c r="D839"/>
+      <c r="E839"/>
+    </row>
+    <row r="840" spans="3:5">
+      <c r="C840"/>
+      <c r="D840"/>
+      <c r="E840"/>
+    </row>
+    <row r="841" spans="3:5">
+      <c r="C841"/>
+      <c r="D841"/>
+      <c r="E841"/>
+    </row>
+    <row r="842" spans="3:5">
+      <c r="C842"/>
+      <c r="D842"/>
+      <c r="E842"/>
+    </row>
+    <row r="843" spans="3:5">
+      <c r="C843"/>
+      <c r="D843"/>
+      <c r="E843"/>
+    </row>
+    <row r="844" spans="3:5">
+      <c r="C844"/>
+      <c r="D844"/>
+      <c r="E844"/>
+    </row>
+    <row r="845" spans="3:5">
+      <c r="C845"/>
+      <c r="D845"/>
+      <c r="E845"/>
+    </row>
+    <row r="846" spans="3:5">
+      <c r="C846"/>
+      <c r="D846"/>
+      <c r="E846"/>
+    </row>
+    <row r="847" spans="3:5">
+      <c r="C847"/>
+      <c r="D847"/>
+      <c r="E847"/>
+    </row>
+    <row r="848" spans="3:5">
+      <c r="C848"/>
+      <c r="D848"/>
+      <c r="E848"/>
+    </row>
+    <row r="849" spans="3:5">
+      <c r="C849"/>
+      <c r="D849"/>
+      <c r="E849"/>
+    </row>
+    <row r="850" spans="3:5">
+      <c r="C850"/>
+      <c r="D850"/>
+      <c r="E850"/>
+    </row>
+    <row r="851" spans="3:5">
+      <c r="C851"/>
+      <c r="D851"/>
+      <c r="E851"/>
+    </row>
+    <row r="852" spans="3:5">
+      <c r="C852"/>
+      <c r="D852"/>
+      <c r="E852"/>
+    </row>
+    <row r="853" spans="3:5">
+      <c r="C853"/>
+      <c r="D853"/>
+      <c r="E853"/>
+    </row>
+    <row r="854" spans="3:5">
+      <c r="C854"/>
+      <c r="D854"/>
+      <c r="E854"/>
+    </row>
+    <row r="855" spans="3:5">
+      <c r="C855"/>
+      <c r="D855"/>
+      <c r="E855"/>
+    </row>
+    <row r="856" spans="3:5">
+      <c r="C856"/>
+      <c r="D856"/>
+      <c r="E856"/>
+    </row>
+    <row r="857" spans="3:5">
+      <c r="C857"/>
+      <c r="D857"/>
+      <c r="E857"/>
+    </row>
+    <row r="858" spans="3:5">
+      <c r="C858"/>
+      <c r="D858"/>
+      <c r="E858"/>
+    </row>
+    <row r="859" spans="3:5">
+      <c r="C859"/>
+      <c r="D859"/>
+      <c r="E859"/>
+    </row>
+    <row r="860" spans="3:5">
+      <c r="C860"/>
+      <c r="D860"/>
+      <c r="E860"/>
+    </row>
+    <row r="861" spans="3:5">
+      <c r="C861"/>
+      <c r="D861"/>
+      <c r="E861"/>
+    </row>
+    <row r="862" spans="3:5">
+      <c r="C862"/>
+      <c r="D862"/>
+      <c r="E862"/>
+    </row>
+    <row r="863" spans="3:5">
+      <c r="C863"/>
+      <c r="D863"/>
+      <c r="E863"/>
+    </row>
+    <row r="864" spans="3:5">
+      <c r="C864"/>
+      <c r="D864"/>
+      <c r="E864"/>
+    </row>
+    <row r="865" spans="3:5">
+      <c r="C865"/>
+      <c r="D865"/>
+      <c r="E865"/>
+    </row>
+    <row r="866" spans="3:5">
+      <c r="C866"/>
+      <c r="D866"/>
+      <c r="E866"/>
+    </row>
+    <row r="867" spans="3:5">
+      <c r="C867"/>
+      <c r="D867"/>
+      <c r="E867"/>
+    </row>
+    <row r="868" spans="3:5">
+      <c r="C868"/>
+      <c r="D868"/>
+      <c r="E868"/>
+    </row>
+    <row r="869" spans="3:5">
+      <c r="C869"/>
+      <c r="D869"/>
+      <c r="E869"/>
+    </row>
+    <row r="870" spans="3:5">
+      <c r="C870"/>
+      <c r="D870"/>
+      <c r="E870"/>
+    </row>
+    <row r="871" spans="3:5">
+      <c r="C871"/>
+      <c r="D871"/>
+      <c r="E871"/>
+    </row>
+    <row r="872" spans="3:5">
+      <c r="C872"/>
+      <c r="D872"/>
+      <c r="E872"/>
+    </row>
+    <row r="873" spans="3:5">
+      <c r="C873"/>
+      <c r="D873"/>
+      <c r="E873"/>
+    </row>
+    <row r="874" spans="3:5">
+      <c r="C874"/>
+      <c r="D874"/>
+      <c r="E874"/>
+    </row>
+    <row r="875" spans="3:5">
+      <c r="C875"/>
+      <c r="D875"/>
+      <c r="E875"/>
+    </row>
+    <row r="876" spans="3:5">
+      <c r="C876"/>
+      <c r="D876"/>
+      <c r="E876"/>
+    </row>
+    <row r="877" spans="3:5">
+      <c r="C877"/>
+      <c r="D877"/>
+      <c r="E877"/>
+    </row>
+    <row r="878" spans="3:5">
+      <c r="C878"/>
+      <c r="D878"/>
+      <c r="E878"/>
+    </row>
+    <row r="879" spans="3:5">
+      <c r="C879"/>
+      <c r="D879"/>
+      <c r="E879"/>
+    </row>
+    <row r="880" spans="3:5">
+      <c r="C880"/>
+      <c r="D880"/>
+      <c r="E880"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <autoFilter ref="B1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
